--- a/EL MIRADOR/Octubre/Octubre - EL MIRADOR .xlsx
+++ b/EL MIRADOR/Octubre/Octubre - EL MIRADOR .xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OneDrive\Desktop\RC CONSORCIO 2025\EL MIRADOR\Octubre\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE6E13F1-967C-4D00-9F6F-DCCA6DB4BA13}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7440213A-B3E5-4825-B891-A094FF0360C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RESUMEN" sheetId="1" r:id="rId1"/>
@@ -1718,7 +1718,7 @@
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="280">
+  <cellXfs count="276">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1944,6 +1944,63 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="16" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="14" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="4" fillId="3" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="18" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="4" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="6" fontId="4" fillId="3" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="8" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="6" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="6" fontId="4" fillId="3" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="23" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="9" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="8" fontId="0" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="6" fontId="0" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="6" fontId="4" fillId="3" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="44" fontId="11" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="14" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="10" fontId="0" fillId="14" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="0" fillId="14" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="11" fillId="14" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="14" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="11" fillId="14" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="4" fontId="0" fillId="14" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="10" fontId="0" fillId="14" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="10" fontId="0" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="0" fillId="5" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="11" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="5" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="11" fillId="5" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="4" fontId="0" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="4" fillId="5" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="10" fontId="0" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="165" fontId="11" fillId="7" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="4" fillId="14" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="4" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="4" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="21" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="10" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="21" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="21" fillId="5" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="4" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -1980,20 +2037,38 @@
     <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="3" borderId="14" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="6" fontId="0" fillId="3" borderId="14" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2016,50 +2091,6 @@
     <xf numFmtId="0" fontId="13" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="16" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="14" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="0" fillId="3" borderId="14" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="6" fontId="0" fillId="3" borderId="14" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="44" fontId="4" fillId="3" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="18" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="4" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="6" fontId="4" fillId="3" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="8" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="6" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
-    <xf numFmtId="6" fontId="4" fillId="3" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="23" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="9" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="8" fontId="0" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="6" fontId="0" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
-    <xf numFmtId="6" fontId="4" fillId="3" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
     <xf numFmtId="1" fontId="20" fillId="5" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -2072,7 +2103,7 @@
     <xf numFmtId="1" fontId="20" fillId="5" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="20" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="20" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="1" fontId="20" fillId="5" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2087,17 +2118,6 @@
     <xf numFmtId="1" fontId="20" fillId="5" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="11" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="14" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="14" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="10" fontId="0" fillId="14" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="0" fillId="14" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="11" fillId="14" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="14" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="11" fillId="14" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="4" fontId="0" fillId="14" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="1" fontId="20" fillId="14" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -2116,33 +2136,9 @@
     <xf numFmtId="1" fontId="20" fillId="14" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="10" fontId="0" fillId="14" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="10" fontId="0" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="0" fillId="5" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="11" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="5" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="11" fillId="5" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="4" fontId="0" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="4" fillId="5" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="10" fontId="0" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="10" fontId="0" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="4" fontId="0" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="165" fontId="11" fillId="7" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="4" fillId="14" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="4" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="4" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="21" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="10" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="21" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="21" fillId="5" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="4" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Millares" xfId="3" builtinId="3"/>
@@ -2689,108 +2685,108 @@
     <row r="11" spans="1:10" hidden="1" x14ac:dyDescent="0.25"/>
     <row r="12" spans="1:10" hidden="1" x14ac:dyDescent="0.25"/>
     <row r="14" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="181" t="s">
+      <c r="A14" s="230" t="s">
         <v>265</v>
       </c>
-      <c r="B14" s="181"/>
-      <c r="C14" s="181"/>
-      <c r="D14" s="181"/>
-      <c r="E14" s="181"/>
-      <c r="F14" s="181"/>
-      <c r="G14" s="181"/>
-      <c r="H14" s="181"/>
-      <c r="I14" s="181"/>
-      <c r="J14" s="181"/>
+      <c r="B14" s="230"/>
+      <c r="C14" s="230"/>
+      <c r="D14" s="230"/>
+      <c r="E14" s="230"/>
+      <c r="F14" s="230"/>
+      <c r="G14" s="230"/>
+      <c r="H14" s="230"/>
+      <c r="I14" s="230"/>
+      <c r="J14" s="230"/>
     </row>
     <row r="15" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="181"/>
-      <c r="B15" s="181"/>
-      <c r="C15" s="181"/>
-      <c r="D15" s="181"/>
-      <c r="E15" s="181"/>
-      <c r="F15" s="181"/>
-      <c r="G15" s="181"/>
-      <c r="H15" s="181"/>
-      <c r="I15" s="181"/>
-      <c r="J15" s="181"/>
+      <c r="A15" s="230"/>
+      <c r="B15" s="230"/>
+      <c r="C15" s="230"/>
+      <c r="D15" s="230"/>
+      <c r="E15" s="230"/>
+      <c r="F15" s="230"/>
+      <c r="G15" s="230"/>
+      <c r="H15" s="230"/>
+      <c r="I15" s="230"/>
+      <c r="J15" s="230"/>
     </row>
     <row r="16" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="181"/>
-      <c r="B16" s="181"/>
-      <c r="C16" s="181"/>
-      <c r="D16" s="181"/>
-      <c r="E16" s="181"/>
-      <c r="F16" s="181"/>
-      <c r="G16" s="181"/>
-      <c r="H16" s="181"/>
-      <c r="I16" s="181"/>
-      <c r="J16" s="181"/>
+      <c r="A16" s="230"/>
+      <c r="B16" s="230"/>
+      <c r="C16" s="230"/>
+      <c r="D16" s="230"/>
+      <c r="E16" s="230"/>
+      <c r="F16" s="230"/>
+      <c r="G16" s="230"/>
+      <c r="H16" s="230"/>
+      <c r="I16" s="230"/>
+      <c r="J16" s="230"/>
     </row>
     <row r="17" spans="1:10" ht="25.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="181"/>
-      <c r="B17" s="181"/>
-      <c r="C17" s="181"/>
-      <c r="D17" s="181"/>
-      <c r="E17" s="181"/>
-      <c r="F17" s="181"/>
-      <c r="G17" s="181"/>
-      <c r="H17" s="181"/>
-      <c r="I17" s="181"/>
-      <c r="J17" s="181"/>
+      <c r="A17" s="230"/>
+      <c r="B17" s="230"/>
+      <c r="C17" s="230"/>
+      <c r="D17" s="230"/>
+      <c r="E17" s="230"/>
+      <c r="F17" s="230"/>
+      <c r="G17" s="230"/>
+      <c r="H17" s="230"/>
+      <c r="I17" s="230"/>
+      <c r="J17" s="230"/>
     </row>
     <row r="18" spans="1:10" ht="47.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="181"/>
-      <c r="B18" s="181"/>
-      <c r="C18" s="181"/>
-      <c r="D18" s="181"/>
-      <c r="E18" s="181"/>
-      <c r="F18" s="181"/>
-      <c r="G18" s="181"/>
-      <c r="H18" s="181"/>
-      <c r="I18" s="181"/>
-      <c r="J18" s="181"/>
+      <c r="A18" s="230"/>
+      <c r="B18" s="230"/>
+      <c r="C18" s="230"/>
+      <c r="D18" s="230"/>
+      <c r="E18" s="230"/>
+      <c r="F18" s="230"/>
+      <c r="G18" s="230"/>
+      <c r="H18" s="230"/>
+      <c r="I18" s="230"/>
+      <c r="J18" s="230"/>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A19" s="2"/>
       <c r="H19" s="100"/>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A20" s="190" t="s">
+      <c r="A20" s="239" t="s">
         <v>328</v>
       </c>
-      <c r="B20" s="190"/>
-      <c r="C20" s="190"/>
-      <c r="D20" s="190"/>
-      <c r="E20" s="190"/>
-      <c r="F20" s="190"/>
-      <c r="G20" s="190"/>
-      <c r="H20" s="190"/>
-      <c r="I20" s="190"/>
-      <c r="J20" s="190"/>
+      <c r="B20" s="239"/>
+      <c r="C20" s="239"/>
+      <c r="D20" s="239"/>
+      <c r="E20" s="239"/>
+      <c r="F20" s="239"/>
+      <c r="G20" s="239"/>
+      <c r="H20" s="239"/>
+      <c r="I20" s="239"/>
+      <c r="J20" s="239"/>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A21" s="190"/>
-      <c r="B21" s="190"/>
-      <c r="C21" s="190"/>
-      <c r="D21" s="190"/>
-      <c r="E21" s="190"/>
-      <c r="F21" s="190"/>
-      <c r="G21" s="190"/>
-      <c r="H21" s="190"/>
-      <c r="I21" s="190"/>
-      <c r="J21" s="190"/>
+      <c r="A21" s="239"/>
+      <c r="B21" s="239"/>
+      <c r="C21" s="239"/>
+      <c r="D21" s="239"/>
+      <c r="E21" s="239"/>
+      <c r="F21" s="239"/>
+      <c r="G21" s="239"/>
+      <c r="H21" s="239"/>
+      <c r="I21" s="239"/>
+      <c r="J21" s="239"/>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A22" s="190"/>
-      <c r="B22" s="190"/>
-      <c r="C22" s="190"/>
-      <c r="D22" s="190"/>
-      <c r="E22" s="190"/>
-      <c r="F22" s="190"/>
-      <c r="G22" s="190"/>
-      <c r="H22" s="190"/>
-      <c r="I22" s="190"/>
-      <c r="J22" s="190"/>
+      <c r="A22" s="239"/>
+      <c r="B22" s="239"/>
+      <c r="C22" s="239"/>
+      <c r="D22" s="239"/>
+      <c r="E22" s="239"/>
+      <c r="F22" s="239"/>
+      <c r="G22" s="239"/>
+      <c r="H22" s="239"/>
+      <c r="I22" s="239"/>
+      <c r="J22" s="239"/>
     </row>
     <row r="23" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="H23" s="100"/>
@@ -3741,7 +3737,7 @@
       <c r="C68" s="6" t="s">
         <v>335</v>
       </c>
-      <c r="D68" s="271">
+      <c r="D68" s="221">
         <v>242436.29</v>
       </c>
       <c r="E68" s="68">
@@ -3793,7 +3789,7 @@
       <c r="C69" s="6" t="s">
         <v>338</v>
       </c>
-      <c r="D69" s="271">
+      <c r="D69" s="221">
         <v>561764.05000000005</v>
       </c>
       <c r="E69" s="68">
@@ -3839,7 +3835,7 @@
       <c r="C70" s="6" t="s">
         <v>336</v>
       </c>
-      <c r="D70" s="272">
+      <c r="D70" s="222">
         <v>200479.44</v>
       </c>
       <c r="E70" s="68">
@@ -3885,7 +3881,7 @@
       <c r="C71" s="6" t="s">
         <v>336</v>
       </c>
-      <c r="D71" s="272">
+      <c r="D71" s="222">
         <v>2000000</v>
       </c>
       <c r="E71" s="68">
@@ -4345,9 +4341,9 @@
       </c>
     </row>
     <row r="82" spans="1:14" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A82" s="188"/>
-      <c r="B82" s="189"/>
-      <c r="C82" s="191"/>
+      <c r="A82" s="237"/>
+      <c r="B82" s="238"/>
+      <c r="C82" s="240"/>
       <c r="D82" s="44"/>
       <c r="E82" s="68"/>
       <c r="F82" s="68"/>
@@ -4370,9 +4366,9 @@
       </c>
     </row>
     <row r="83" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A83" s="188"/>
-      <c r="B83" s="189"/>
-      <c r="C83" s="191"/>
+      <c r="A83" s="237"/>
+      <c r="B83" s="238"/>
+      <c r="C83" s="240"/>
       <c r="D83" s="44"/>
       <c r="E83" s="68"/>
       <c r="F83" s="68"/>
@@ -4472,31 +4468,31 @@
       <c r="B87" s="34"/>
       <c r="C87" s="34"/>
       <c r="D87" s="42">
-        <f>SUM(D68:D86)</f>
+        <f t="shared" ref="D87:J87" si="19">SUM(D68:D86)</f>
         <v>5804281.7000000002</v>
       </c>
       <c r="E87" s="42">
-        <f>SUM(E68:E86)</f>
+        <f t="shared" si="19"/>
         <v>5440432.9895600006</v>
       </c>
       <c r="F87" s="42">
-        <f>SUM(F68:F86)</f>
+        <f t="shared" si="19"/>
         <v>57787.736364000004</v>
       </c>
       <c r="G87" s="42">
-        <f>SUM(G68:G86)</f>
+        <f t="shared" si="19"/>
         <v>68489.169024000003</v>
       </c>
       <c r="H87" s="42">
-        <f>SUM(H68:H86)</f>
+        <f t="shared" si="19"/>
         <v>64743.667592999991</v>
       </c>
       <c r="I87" s="42">
-        <f>SUM(I68:I86)</f>
+        <f t="shared" si="19"/>
         <v>79725.673317000008</v>
       </c>
       <c r="J87" s="42">
-        <f>SUM(J68:J86)</f>
+        <f t="shared" si="19"/>
         <v>93102.464141999997</v>
       </c>
       <c r="K87" s="43">
@@ -4675,27 +4671,27 @@
         <v>467500</v>
       </c>
       <c r="E97" s="42">
-        <f t="shared" ref="E97:J97" si="19">SUM(E91:E96)</f>
+        <f t="shared" ref="E97:J97" si="20">SUM(E91:E96)</f>
         <v>435710</v>
       </c>
       <c r="F97" s="42">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>5049</v>
       </c>
       <c r="G97" s="42">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>5984</v>
       </c>
       <c r="H97" s="42">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>5656.75</v>
       </c>
       <c r="I97" s="42">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>6965.75</v>
       </c>
       <c r="J97" s="42">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>8134.4999999999991</v>
       </c>
       <c r="K97" s="43">
@@ -4831,19 +4827,19 @@
         <v>702448.4</v>
       </c>
       <c r="F104" s="42">
-        <f t="shared" ref="F104:I104" si="20">SUM(F101:F103)</f>
+        <f t="shared" ref="F104:I104" si="21">SUM(F101:F103)</f>
         <v>8139.96</v>
       </c>
       <c r="G104" s="42">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>9647.36</v>
       </c>
       <c r="H104" s="42">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>9119.77</v>
       </c>
       <c r="I104" s="42">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>11230.13</v>
       </c>
       <c r="J104" s="42">
@@ -4939,27 +4935,27 @@
         <v>162451.64000000001</v>
       </c>
       <c r="E107" s="67">
-        <f t="shared" ref="E107:J107" si="21">SUM(E105:E106)</f>
+        <f t="shared" ref="E107:J107" si="22">SUM(E105:E106)</f>
         <v>151404.92848000003</v>
       </c>
       <c r="F107" s="67">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>1754.4777120000003</v>
       </c>
       <c r="G107" s="67">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>2079.3809920000003</v>
       </c>
       <c r="H107" s="67">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>1965.6648440000001</v>
       </c>
       <c r="I107" s="67">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>2420.5294360000003</v>
       </c>
       <c r="J107" s="67">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>2826.6585359999999</v>
       </c>
       <c r="K107" s="43">
@@ -4991,36 +4987,36 @@
       <c r="B109" s="107"/>
       <c r="C109" s="107"/>
       <c r="D109" s="108">
-        <f>11000000-9608383.86</f>
-        <v>1391616.1400000006</v>
+        <f>12000000-9608383.86</f>
+        <v>2391616.1400000006</v>
       </c>
       <c r="E109" s="131">
         <f>D109*93.2%</f>
-        <v>1296986.2424800007</v>
+        <v>2228986.2424800005</v>
       </c>
       <c r="F109" s="131">
         <f>$D109*1.08%</f>
-        <v>15029.454312000007</v>
+        <v>25829.454312000009</v>
       </c>
       <c r="G109" s="131">
         <f>$D109*1.28%</f>
-        <v>17812.686592000009</v>
+        <v>30612.686592000009</v>
       </c>
       <c r="H109" s="131">
         <f>$D109*1.21%</f>
-        <v>16838.555294000005</v>
+        <v>28938.555294000005</v>
       </c>
       <c r="I109" s="131">
         <f>$D109*1.49%</f>
-        <v>20735.08048600001</v>
+        <v>35635.080486000006</v>
       </c>
       <c r="J109" s="132">
         <f>D109*1.74%</f>
-        <v>24214.120836000009</v>
+        <v>41614.120836000009</v>
       </c>
       <c r="K109" s="43">
         <f>E109+J109+F109+G109+H109+I109</f>
-        <v>1391616.1400000008</v>
+        <v>2391616.1400000006</v>
       </c>
       <c r="L109" s="69" t="str">
         <f>IF(D109=K109, "", "Error")</f>
@@ -5048,36 +5044,36 @@
       <c r="B111" s="11"/>
       <c r="C111" s="4"/>
       <c r="D111" s="91">
-        <f>SUM(D109+D57+D52+D107+D104+D97+D87+D66+D47+D42+D61)</f>
-        <v>11000000</v>
+        <f t="shared" ref="D111:J111" si="23">SUM(D109+D57+D52+D107+D104+D97+D87+D66+D47+D42+D61)</f>
+        <v>12000000</v>
       </c>
       <c r="E111" s="91">
-        <f>SUM(E109+E57+E52+E107+E104+E97+E87+E66+E47+E42+E61)</f>
-        <v>10282842.445160002</v>
+        <f t="shared" si="23"/>
+        <v>11214842.44516</v>
       </c>
       <c r="F111" s="91">
-        <f>SUM(F109+F57+F52+F107+F104+F97+F87+F66+F47+F42+F61)</f>
-        <v>113901.49400400001</v>
+        <f t="shared" si="23"/>
+        <v>124701.49400400001</v>
       </c>
       <c r="G111" s="91">
-        <f>SUM(G109+G57+G52+G107+G104+G97+G87+G66+G47+G42+G61)</f>
-        <v>134994.36326400004</v>
+        <f t="shared" si="23"/>
+        <v>147794.36326400004</v>
       </c>
       <c r="H111" s="91">
-        <f>SUM(H109+H57+H52+H107+H104+H97+H87+H66+H47+H42+H61)</f>
-        <v>127611.859023</v>
+        <f t="shared" si="23"/>
+        <v>139711.859023</v>
       </c>
       <c r="I111" s="91">
-        <f>SUM(I109+I57+I52+I107+I104+I97+I87+I66+I47+I42+I61)</f>
-        <v>157141.87598700004</v>
+        <f t="shared" si="23"/>
+        <v>172041.87598700004</v>
       </c>
       <c r="J111" s="91">
-        <f>SUM(J109+J57+J52+J107+J104+J97+J87+J66+J47+J42+J61)</f>
-        <v>183507.96256200003</v>
+        <f t="shared" si="23"/>
+        <v>200907.96256200003</v>
       </c>
       <c r="K111" s="61">
         <f>E111+J111+F111+G111+H111+I111</f>
-        <v>11000000.000000002</v>
+        <v>12000000</v>
       </c>
       <c r="L111" s="69" t="str">
         <f>IF(D111=K111, "", "Error")</f>
@@ -5270,12 +5266,12 @@
       <c r="I126" s="60"/>
     </row>
     <row r="127" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A127" s="186" t="s">
+      <c r="A127" s="235" t="s">
         <v>36</v>
       </c>
-      <c r="B127" s="187"/>
-      <c r="C127" s="187"/>
-      <c r="D127" s="187"/>
+      <c r="B127" s="236"/>
+      <c r="C127" s="236"/>
+      <c r="D127" s="236"/>
       <c r="E127" s="82" t="s">
         <v>11</v>
       </c>
@@ -5296,8 +5292,8 @@
       </c>
     </row>
     <row r="128" spans="1:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A128" s="188"/>
-      <c r="B128" s="189"/>
+      <c r="A128" s="237"/>
+      <c r="B128" s="238"/>
       <c r="C128" s="84"/>
       <c r="D128" s="44"/>
       <c r="E128" s="68">
@@ -5311,8 +5307,8 @@
       <c r="J128" s="58"/>
     </row>
     <row r="129" spans="1:13" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A129" s="188"/>
-      <c r="B129" s="189"/>
+      <c r="A129" s="237"/>
+      <c r="B129" s="238"/>
       <c r="C129" s="84"/>
       <c r="D129" s="44"/>
       <c r="E129" s="68"/>
@@ -5323,11 +5319,11 @@
       <c r="J129" s="58"/>
     </row>
     <row r="130" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A130" s="183" t="s">
+      <c r="A130" s="232" t="s">
         <v>17</v>
       </c>
-      <c r="B130" s="184"/>
-      <c r="C130" s="185"/>
+      <c r="B130" s="233"/>
+      <c r="C130" s="234"/>
       <c r="D130" s="81">
         <f>SUM(D128:D129)</f>
         <v>0</v>
@@ -5366,7 +5362,7 @@
       </c>
       <c r="B133" s="39">
         <f>D111</f>
-        <v>11000000</v>
+        <v>12000000</v>
       </c>
     </row>
     <row r="134" spans="1:13" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -5377,22 +5373,22 @@
         <f>D111-D109</f>
         <v>9608383.8599999994</v>
       </c>
-      <c r="D134" s="192" t="s">
+      <c r="D134" s="241" t="s">
         <v>323</v>
       </c>
-      <c r="E134" s="192"/>
-      <c r="F134" s="192"/>
-      <c r="G134" s="192"/>
-      <c r="H134" s="192"/>
-      <c r="I134" s="192"/>
+      <c r="E134" s="241"/>
+      <c r="F134" s="241"/>
+      <c r="G134" s="241"/>
+      <c r="H134" s="241"/>
+      <c r="I134" s="241"/>
     </row>
     <row r="135" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="D135" s="192"/>
-      <c r="E135" s="192"/>
-      <c r="F135" s="192"/>
-      <c r="G135" s="192"/>
-      <c r="H135" s="192"/>
-      <c r="I135" s="192"/>
+      <c r="D135" s="241"/>
+      <c r="E135" s="241"/>
+      <c r="F135" s="241"/>
+      <c r="G135" s="241"/>
+      <c r="H135" s="241"/>
+      <c r="I135" s="241"/>
     </row>
     <row r="136" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A136" s="16" t="s">
@@ -5400,12 +5396,12 @@
       </c>
       <c r="B136" s="17"/>
       <c r="C136" s="18"/>
-      <c r="D136" s="192"/>
-      <c r="E136" s="192"/>
-      <c r="F136" s="192"/>
-      <c r="G136" s="192"/>
-      <c r="H136" s="192"/>
-      <c r="I136" s="192"/>
+      <c r="D136" s="241"/>
+      <c r="E136" s="241"/>
+      <c r="F136" s="241"/>
+      <c r="G136" s="241"/>
+      <c r="H136" s="241"/>
+      <c r="I136" s="241"/>
     </row>
     <row r="137" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A137" s="19" t="s">
@@ -5415,12 +5411,12 @@
         <v>-1505552.0204280028</v>
       </c>
       <c r="C137" s="20"/>
-      <c r="D137" s="192"/>
-      <c r="E137" s="192"/>
-      <c r="F137" s="192"/>
-      <c r="G137" s="192"/>
-      <c r="H137" s="192"/>
-      <c r="I137" s="192"/>
+      <c r="D137" s="241"/>
+      <c r="E137" s="241"/>
+      <c r="F137" s="241"/>
+      <c r="G137" s="241"/>
+      <c r="H137" s="241"/>
+      <c r="I137" s="241"/>
     </row>
     <row r="138" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A138" s="21" t="s">
@@ -5433,12 +5429,12 @@
       <c r="C138" s="20" t="s">
         <v>23</v>
       </c>
-      <c r="D138" s="192"/>
-      <c r="E138" s="192"/>
-      <c r="F138" s="192"/>
-      <c r="G138" s="192"/>
-      <c r="H138" s="192"/>
-      <c r="I138" s="192"/>
+      <c r="D138" s="241"/>
+      <c r="E138" s="241"/>
+      <c r="F138" s="241"/>
+      <c r="G138" s="241"/>
+      <c r="H138" s="241"/>
+      <c r="I138" s="241"/>
     </row>
     <row r="139" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A139" s="21" t="s">
@@ -5449,12 +5445,12 @@
         <v>-9608383.8599999994</v>
       </c>
       <c r="C139" s="18"/>
-      <c r="D139" s="192"/>
-      <c r="E139" s="192"/>
-      <c r="F139" s="192"/>
-      <c r="G139" s="192"/>
-      <c r="H139" s="192"/>
-      <c r="I139" s="192"/>
+      <c r="D139" s="241"/>
+      <c r="E139" s="241"/>
+      <c r="F139" s="241"/>
+      <c r="G139" s="241"/>
+      <c r="H139" s="241"/>
+      <c r="I139" s="241"/>
       <c r="K139" s="44"/>
     </row>
     <row r="140" spans="1:13" x14ac:dyDescent="0.25">
@@ -5466,12 +5462,12 @@
         <v>0</v>
       </c>
       <c r="C140" s="18"/>
-      <c r="D140" s="192"/>
-      <c r="E140" s="192"/>
-      <c r="F140" s="192"/>
-      <c r="G140" s="192"/>
-      <c r="H140" s="192"/>
-      <c r="I140" s="192"/>
+      <c r="D140" s="241"/>
+      <c r="E140" s="241"/>
+      <c r="F140" s="241"/>
+      <c r="G140" s="241"/>
+      <c r="H140" s="241"/>
+      <c r="I140" s="241"/>
       <c r="K140" s="52"/>
     </row>
     <row r="141" spans="1:13" x14ac:dyDescent="0.25">
@@ -5483,12 +5479,12 @@
         <v>0</v>
       </c>
       <c r="C141" s="18"/>
-      <c r="D141" s="192"/>
-      <c r="E141" s="192"/>
-      <c r="F141" s="192"/>
-      <c r="G141" s="192"/>
-      <c r="H141" s="192"/>
-      <c r="I141" s="192"/>
+      <c r="D141" s="241"/>
+      <c r="E141" s="241"/>
+      <c r="F141" s="241"/>
+      <c r="G141" s="241"/>
+      <c r="H141" s="241"/>
+      <c r="I141" s="241"/>
       <c r="K141" s="52"/>
     </row>
     <row r="142" spans="1:13" x14ac:dyDescent="0.25">
@@ -5500,12 +5496,12 @@
         <v>0</v>
       </c>
       <c r="C142" s="22"/>
-      <c r="D142" s="192"/>
-      <c r="E142" s="192"/>
-      <c r="F142" s="192"/>
-      <c r="G142" s="192"/>
-      <c r="H142" s="192"/>
-      <c r="I142" s="192"/>
+      <c r="D142" s="241"/>
+      <c r="E142" s="241"/>
+      <c r="F142" s="241"/>
+      <c r="G142" s="241"/>
+      <c r="H142" s="241"/>
+      <c r="I142" s="241"/>
     </row>
     <row r="143" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A143" s="21" t="s">
@@ -5515,12 +5511,12 @@
         <v>0</v>
       </c>
       <c r="C143" s="22"/>
-      <c r="D143" s="192"/>
-      <c r="E143" s="192"/>
-      <c r="F143" s="192"/>
-      <c r="G143" s="192"/>
-      <c r="H143" s="192"/>
-      <c r="I143" s="192"/>
+      <c r="D143" s="241"/>
+      <c r="E143" s="241"/>
+      <c r="F143" s="241"/>
+      <c r="G143" s="241"/>
+      <c r="H143" s="241"/>
+      <c r="I143" s="241"/>
     </row>
     <row r="144" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A144" s="21" t="s">
@@ -5531,27 +5527,27 @@
         <v>-206000</v>
       </c>
       <c r="C144" s="22"/>
-      <c r="D144" s="192"/>
-      <c r="E144" s="192"/>
-      <c r="F144" s="192"/>
-      <c r="G144" s="192"/>
-      <c r="H144" s="192"/>
-      <c r="I144" s="192"/>
+      <c r="D144" s="241"/>
+      <c r="E144" s="241"/>
+      <c r="F144" s="241"/>
+      <c r="G144" s="241"/>
+      <c r="H144" s="241"/>
+      <c r="I144" s="241"/>
     </row>
     <row r="145" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A145" s="21" t="s">
         <v>342</v>
       </c>
-      <c r="B145" s="237">
+      <c r="B145" s="196">
         <v>400000</v>
       </c>
       <c r="C145" s="22"/>
-      <c r="D145" s="192"/>
-      <c r="E145" s="192"/>
-      <c r="F145" s="192"/>
-      <c r="G145" s="192"/>
-      <c r="H145" s="192"/>
-      <c r="I145" s="192"/>
+      <c r="D145" s="241"/>
+      <c r="E145" s="241"/>
+      <c r="F145" s="241"/>
+      <c r="G145" s="241"/>
+      <c r="H145" s="241"/>
+      <c r="I145" s="241"/>
     </row>
     <row r="146" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A146" s="19" t="s">
@@ -5562,22 +5558,22 @@
         <v>-979600.31345474347</v>
       </c>
       <c r="C146" s="70"/>
-      <c r="D146" s="192"/>
-      <c r="E146" s="192"/>
-      <c r="F146" s="192"/>
-      <c r="G146" s="192"/>
-      <c r="H146" s="192"/>
-      <c r="I146" s="192"/>
+      <c r="D146" s="241"/>
+      <c r="E146" s="241"/>
+      <c r="F146" s="241"/>
+      <c r="G146" s="241"/>
+      <c r="H146" s="241"/>
+      <c r="I146" s="241"/>
     </row>
     <row r="147" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A147" s="22"/>
       <c r="C147" s="18"/>
-      <c r="D147" s="192"/>
-      <c r="E147" s="192"/>
-      <c r="F147" s="192"/>
-      <c r="G147" s="192"/>
-      <c r="H147" s="192"/>
-      <c r="I147" s="192"/>
+      <c r="D147" s="241"/>
+      <c r="E147" s="241"/>
+      <c r="F147" s="241"/>
+      <c r="G147" s="241"/>
+      <c r="H147" s="241"/>
+      <c r="I147" s="241"/>
     </row>
     <row r="148" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A148" s="16" t="s">
@@ -5585,12 +5581,12 @@
       </c>
       <c r="B148" s="8"/>
       <c r="C148" s="18"/>
-      <c r="D148" s="192"/>
-      <c r="E148" s="192"/>
-      <c r="F148" s="192"/>
-      <c r="G148" s="192"/>
-      <c r="H148" s="192"/>
-      <c r="I148" s="192"/>
+      <c r="D148" s="241"/>
+      <c r="E148" s="241"/>
+      <c r="F148" s="241"/>
+      <c r="G148" s="241"/>
+      <c r="H148" s="241"/>
+      <c r="I148" s="241"/>
     </row>
     <row r="149" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A149" s="19"/>
@@ -5695,50 +5691,50 @@
       <c r="R162" s="9"/>
     </row>
     <row r="165" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B165" s="182"/>
-      <c r="C165" s="182"/>
-      <c r="D165" s="182"/>
-      <c r="E165" s="182"/>
+      <c r="B165" s="231"/>
+      <c r="C165" s="231"/>
+      <c r="D165" s="231"/>
+      <c r="E165" s="231"/>
       <c r="F165" s="95"/>
       <c r="G165" s="95"/>
       <c r="H165" s="95"/>
       <c r="I165" s="95"/>
     </row>
     <row r="166" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B166" s="182"/>
-      <c r="C166" s="182"/>
-      <c r="D166" s="182"/>
-      <c r="E166" s="182"/>
+      <c r="B166" s="231"/>
+      <c r="C166" s="231"/>
+      <c r="D166" s="231"/>
+      <c r="E166" s="231"/>
       <c r="F166" s="95"/>
       <c r="G166" s="95"/>
       <c r="H166" s="95"/>
       <c r="I166" s="95"/>
     </row>
     <row r="167" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B167" s="182"/>
-      <c r="C167" s="182"/>
-      <c r="D167" s="182"/>
-      <c r="E167" s="182"/>
+      <c r="B167" s="231"/>
+      <c r="C167" s="231"/>
+      <c r="D167" s="231"/>
+      <c r="E167" s="231"/>
       <c r="F167" s="95"/>
       <c r="G167" s="95"/>
       <c r="H167" s="95"/>
       <c r="I167" s="95"/>
     </row>
     <row r="168" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B168" s="182"/>
-      <c r="C168" s="182"/>
-      <c r="D168" s="182"/>
-      <c r="E168" s="182"/>
+      <c r="B168" s="231"/>
+      <c r="C168" s="231"/>
+      <c r="D168" s="231"/>
+      <c r="E168" s="231"/>
       <c r="F168" s="95"/>
       <c r="G168" s="95"/>
       <c r="H168" s="95"/>
       <c r="I168" s="95"/>
     </row>
     <row r="169" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B169" s="182"/>
-      <c r="C169" s="182"/>
-      <c r="D169" s="182"/>
-      <c r="E169" s="182"/>
+      <c r="B169" s="231"/>
+      <c r="C169" s="231"/>
+      <c r="D169" s="231"/>
+      <c r="E169" s="231"/>
       <c r="F169" s="95"/>
       <c r="G169" s="95"/>
       <c r="H169" s="95"/>
@@ -5787,273 +5783,273 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A1" s="210"/>
-      <c r="B1" s="211"/>
-      <c r="C1" s="211"/>
-      <c r="D1" s="211"/>
-      <c r="E1" s="211"/>
-      <c r="F1" s="211" t="s">
+      <c r="A1" s="181"/>
+      <c r="B1" s="182"/>
+      <c r="C1" s="182"/>
+      <c r="D1" s="182"/>
+      <c r="E1" s="182"/>
+      <c r="F1" s="182" t="s">
         <v>314</v>
       </c>
-      <c r="G1" s="211"/>
-      <c r="H1" s="211"/>
-      <c r="I1" s="211"/>
-      <c r="J1" s="211"/>
-      <c r="K1" s="211" t="s">
+      <c r="G1" s="182"/>
+      <c r="H1" s="182"/>
+      <c r="I1" s="182"/>
+      <c r="J1" s="182"/>
+      <c r="K1" s="182" t="s">
         <v>43</v>
       </c>
-      <c r="L1" s="212">
+      <c r="L1" s="251">
         <f>RESUMEN!D111-RESUMEN!D109</f>
         <v>9608383.8599999994</v>
       </c>
-      <c r="M1" s="213"/>
-      <c r="N1" s="214"/>
+      <c r="M1" s="252"/>
+      <c r="N1" s="183"/>
       <c r="O1" s="59"/>
     </row>
     <row r="2" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A2" s="215"/>
-      <c r="B2" s="216"/>
-      <c r="C2" s="216"/>
-      <c r="D2" s="216"/>
-      <c r="E2" s="216"/>
-      <c r="F2" s="216" t="s">
+      <c r="A2" s="184"/>
+      <c r="B2" s="7"/>
+      <c r="C2" s="7"/>
+      <c r="D2" s="7"/>
+      <c r="E2" s="7"/>
+      <c r="F2" s="7" t="s">
         <v>313</v>
       </c>
-      <c r="G2" s="216"/>
-      <c r="H2" s="216"/>
-      <c r="I2" s="216"/>
-      <c r="J2" s="216"/>
-      <c r="K2" s="216" t="s">
+      <c r="G2" s="7"/>
+      <c r="H2" s="7"/>
+      <c r="I2" s="7"/>
+      <c r="J2" s="7"/>
+      <c r="K2" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="L2" s="216"/>
-      <c r="M2" s="217">
-        <v>11000000</v>
-      </c>
-      <c r="N2" s="218"/>
+      <c r="L2" s="7"/>
+      <c r="M2" s="185">
+        <v>12000000</v>
+      </c>
+      <c r="N2" s="186"/>
       <c r="O2" s="59"/>
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A3" s="215" t="str">
+      <c r="A3" s="184" t="str">
         <f>RESUMEN!C5</f>
         <v>PERÍODO: OCTUBRE</v>
       </c>
-      <c r="B3" s="216"/>
-      <c r="C3" s="216"/>
-      <c r="D3" s="216"/>
-      <c r="E3" s="216"/>
-      <c r="F3" s="216" t="s">
+      <c r="B3" s="7"/>
+      <c r="C3" s="7"/>
+      <c r="D3" s="7"/>
+      <c r="E3" s="7"/>
+      <c r="F3" s="7" t="s">
         <v>315</v>
       </c>
-      <c r="G3" s="216"/>
-      <c r="H3" s="216"/>
-      <c r="I3" s="216"/>
-      <c r="J3" s="219"/>
-      <c r="K3" s="216"/>
-      <c r="L3" s="216"/>
-      <c r="M3" s="220"/>
-      <c r="N3" s="221"/>
+      <c r="G3" s="7"/>
+      <c r="H3" s="7"/>
+      <c r="I3" s="7"/>
+      <c r="J3" s="187"/>
+      <c r="K3" s="7"/>
+      <c r="L3" s="7"/>
+      <c r="M3" s="188"/>
+      <c r="N3" s="189"/>
       <c r="O3" s="15"/>
     </row>
     <row r="4" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="222"/>
-      <c r="B4" s="223"/>
-      <c r="C4" s="223"/>
-      <c r="D4" s="223"/>
-      <c r="E4" s="223"/>
-      <c r="F4" s="223"/>
-      <c r="G4" s="223"/>
-      <c r="H4" s="223"/>
-      <c r="I4" s="223"/>
-      <c r="J4" s="224"/>
-      <c r="K4" s="223"/>
-      <c r="L4" s="223"/>
-      <c r="M4" s="225"/>
-      <c r="N4" s="226"/>
+      <c r="A4" s="190"/>
+      <c r="B4" s="191"/>
+      <c r="C4" s="191"/>
+      <c r="D4" s="191"/>
+      <c r="E4" s="191"/>
+      <c r="F4" s="191"/>
+      <c r="G4" s="191"/>
+      <c r="H4" s="191"/>
+      <c r="I4" s="191"/>
+      <c r="J4" s="192"/>
+      <c r="K4" s="191"/>
+      <c r="L4" s="191"/>
+      <c r="M4" s="193"/>
+      <c r="N4" s="194"/>
       <c r="O4" s="15"/>
     </row>
     <row r="5" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A5" s="7"/>
       <c r="B5" s="7"/>
-      <c r="C5" s="227" t="s">
+      <c r="C5" s="260" t="s">
         <v>337</v>
       </c>
-      <c r="D5" s="228"/>
-      <c r="E5" s="228"/>
-      <c r="F5" s="228"/>
-      <c r="G5" s="228"/>
-      <c r="H5" s="228"/>
-      <c r="I5" s="228"/>
-      <c r="J5" s="228"/>
-      <c r="K5" s="228"/>
-      <c r="L5" s="228"/>
-      <c r="M5" s="228"/>
-      <c r="N5" s="229"/>
+      <c r="D5" s="261"/>
+      <c r="E5" s="261"/>
+      <c r="F5" s="261"/>
+      <c r="G5" s="261"/>
+      <c r="H5" s="261"/>
+      <c r="I5" s="261"/>
+      <c r="J5" s="261"/>
+      <c r="K5" s="261"/>
+      <c r="L5" s="261"/>
+      <c r="M5" s="261"/>
+      <c r="N5" s="262"/>
       <c r="O5" s="15"/>
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A6" s="7"/>
       <c r="B6" s="7"/>
-      <c r="C6" s="230"/>
-      <c r="D6" s="231"/>
-      <c r="E6" s="231"/>
-      <c r="F6" s="231"/>
-      <c r="G6" s="231"/>
-      <c r="H6" s="231"/>
-      <c r="I6" s="231"/>
-      <c r="J6" s="231"/>
-      <c r="K6" s="231"/>
-      <c r="L6" s="231"/>
-      <c r="M6" s="231"/>
-      <c r="N6" s="232"/>
+      <c r="C6" s="263"/>
+      <c r="D6" s="264"/>
+      <c r="E6" s="264"/>
+      <c r="F6" s="264"/>
+      <c r="G6" s="264"/>
+      <c r="H6" s="264"/>
+      <c r="I6" s="264"/>
+      <c r="J6" s="264"/>
+      <c r="K6" s="264"/>
+      <c r="L6" s="264"/>
+      <c r="M6" s="264"/>
+      <c r="N6" s="265"/>
       <c r="O6" s="15"/>
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A7" s="7"/>
       <c r="B7" s="7"/>
-      <c r="C7" s="230"/>
-      <c r="D7" s="231"/>
-      <c r="E7" s="231"/>
-      <c r="F7" s="231"/>
-      <c r="G7" s="231"/>
-      <c r="H7" s="231"/>
-      <c r="I7" s="231"/>
-      <c r="J7" s="231"/>
-      <c r="K7" s="231"/>
-      <c r="L7" s="231"/>
-      <c r="M7" s="231"/>
-      <c r="N7" s="232"/>
+      <c r="C7" s="263"/>
+      <c r="D7" s="264"/>
+      <c r="E7" s="264"/>
+      <c r="F7" s="264"/>
+      <c r="G7" s="264"/>
+      <c r="H7" s="264"/>
+      <c r="I7" s="264"/>
+      <c r="J7" s="264"/>
+      <c r="K7" s="264"/>
+      <c r="L7" s="264"/>
+      <c r="M7" s="264"/>
+      <c r="N7" s="265"/>
       <c r="O7" s="15"/>
     </row>
     <row r="8" spans="1:18" ht="27.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="7"/>
       <c r="B8" s="7"/>
-      <c r="C8" s="233"/>
-      <c r="D8" s="234"/>
-      <c r="E8" s="234"/>
-      <c r="F8" s="234"/>
-      <c r="G8" s="234"/>
-      <c r="H8" s="234"/>
-      <c r="I8" s="234"/>
-      <c r="J8" s="234"/>
-      <c r="K8" s="234"/>
-      <c r="L8" s="234"/>
-      <c r="M8" s="234"/>
-      <c r="N8" s="235"/>
+      <c r="C8" s="266"/>
+      <c r="D8" s="267"/>
+      <c r="E8" s="267"/>
+      <c r="F8" s="267"/>
+      <c r="G8" s="267"/>
+      <c r="H8" s="267"/>
+      <c r="I8" s="267"/>
+      <c r="J8" s="267"/>
+      <c r="K8" s="267"/>
+      <c r="L8" s="267"/>
+      <c r="M8" s="267"/>
+      <c r="N8" s="268"/>
       <c r="P8" s="86">
         <f>L1-K133</f>
-        <v>-1338773.6948400009</v>
+        <v>-2336773.6948400009</v>
       </c>
     </row>
     <row r="9" spans="1:18" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="7"/>
       <c r="B9" s="7"/>
-      <c r="C9" s="247" t="s">
+      <c r="C9" s="269" t="s">
         <v>355</v>
       </c>
-      <c r="D9" s="248"/>
-      <c r="E9" s="248"/>
-      <c r="F9" s="248"/>
-      <c r="G9" s="248"/>
-      <c r="H9" s="248"/>
-      <c r="I9" s="248"/>
-      <c r="J9" s="248"/>
-      <c r="K9" s="248"/>
-      <c r="L9" s="248"/>
-      <c r="M9" s="248"/>
-      <c r="N9" s="249"/>
+      <c r="D9" s="270"/>
+      <c r="E9" s="270"/>
+      <c r="F9" s="270"/>
+      <c r="G9" s="270"/>
+      <c r="H9" s="270"/>
+      <c r="I9" s="270"/>
+      <c r="J9" s="270"/>
+      <c r="K9" s="270"/>
+      <c r="L9" s="270"/>
+      <c r="M9" s="270"/>
+      <c r="N9" s="271"/>
       <c r="P9" s="86"/>
     </row>
     <row r="10" spans="1:18" ht="27.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="7"/>
       <c r="B10" s="7"/>
-      <c r="C10" s="250"/>
-      <c r="D10" s="251"/>
-      <c r="E10" s="251"/>
-      <c r="F10" s="251"/>
-      <c r="G10" s="251"/>
-      <c r="H10" s="251"/>
-      <c r="I10" s="251"/>
-      <c r="J10" s="251"/>
-      <c r="K10" s="251"/>
-      <c r="L10" s="251"/>
-      <c r="M10" s="251"/>
-      <c r="N10" s="252"/>
+      <c r="C10" s="272"/>
+      <c r="D10" s="273"/>
+      <c r="E10" s="273"/>
+      <c r="F10" s="273"/>
+      <c r="G10" s="273"/>
+      <c r="H10" s="273"/>
+      <c r="I10" s="273"/>
+      <c r="J10" s="273"/>
+      <c r="K10" s="273"/>
+      <c r="L10" s="273"/>
+      <c r="M10" s="273"/>
+      <c r="N10" s="274"/>
       <c r="P10" s="86"/>
     </row>
     <row r="11" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="194" t="s">
+      <c r="A11" s="242" t="s">
         <v>9</v>
       </c>
-      <c r="B11" s="205" t="s">
+      <c r="B11" s="244" t="s">
         <v>10</v>
       </c>
-      <c r="C11" s="194" t="s">
+      <c r="C11" s="242" t="s">
         <v>11</v>
       </c>
-      <c r="D11" s="207" t="s">
+      <c r="D11" s="246" t="s">
         <v>12</v>
       </c>
-      <c r="E11" s="207" t="s">
+      <c r="E11" s="246" t="s">
         <v>274</v>
       </c>
-      <c r="F11" s="194" t="s">
+      <c r="F11" s="242" t="s">
         <v>27</v>
       </c>
-      <c r="G11" s="194" t="s">
+      <c r="G11" s="242" t="s">
         <v>13</v>
       </c>
-      <c r="H11" s="194" t="s">
+      <c r="H11" s="242" t="s">
         <v>14</v>
       </c>
-      <c r="I11" s="198" t="s">
+      <c r="I11" s="253" t="s">
         <v>15</v>
       </c>
-      <c r="J11" s="200" t="s">
+      <c r="J11" s="255" t="s">
         <v>16</v>
       </c>
-      <c r="K11" s="200" t="s">
+      <c r="K11" s="255" t="s">
         <v>18</v>
       </c>
-      <c r="L11" s="203" t="s">
+      <c r="L11" s="258" t="s">
         <v>42</v>
       </c>
-      <c r="M11" s="200" t="s">
+      <c r="M11" s="255" t="s">
         <v>285</v>
       </c>
-      <c r="N11" s="200" t="s">
+      <c r="N11" s="255" t="s">
         <v>284</v>
       </c>
     </row>
     <row r="12" spans="1:18" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="195"/>
-      <c r="B12" s="206"/>
-      <c r="C12" s="195"/>
-      <c r="D12" s="208"/>
-      <c r="E12" s="208"/>
-      <c r="F12" s="195"/>
-      <c r="G12" s="195"/>
-      <c r="H12" s="195"/>
-      <c r="I12" s="199"/>
-      <c r="J12" s="201"/>
-      <c r="K12" s="201"/>
-      <c r="L12" s="204"/>
-      <c r="M12" s="201"/>
-      <c r="N12" s="201"/>
+      <c r="A12" s="243"/>
+      <c r="B12" s="245"/>
+      <c r="C12" s="243"/>
+      <c r="D12" s="247"/>
+      <c r="E12" s="247"/>
+      <c r="F12" s="243"/>
+      <c r="G12" s="243"/>
+      <c r="H12" s="243"/>
+      <c r="I12" s="254"/>
+      <c r="J12" s="256"/>
+      <c r="K12" s="256"/>
+      <c r="L12" s="259"/>
+      <c r="M12" s="256"/>
+      <c r="N12" s="256"/>
     </row>
     <row r="13" spans="1:18" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="195"/>
-      <c r="B13" s="206"/>
-      <c r="C13" s="195"/>
-      <c r="D13" s="208"/>
-      <c r="E13" s="208"/>
-      <c r="F13" s="195"/>
-      <c r="G13" s="195"/>
-      <c r="H13" s="195"/>
-      <c r="I13" s="199"/>
-      <c r="J13" s="201"/>
-      <c r="K13" s="202"/>
-      <c r="L13" s="204"/>
+      <c r="A13" s="243"/>
+      <c r="B13" s="245"/>
+      <c r="C13" s="243"/>
+      <c r="D13" s="247"/>
+      <c r="E13" s="247"/>
+      <c r="F13" s="243"/>
+      <c r="G13" s="243"/>
+      <c r="H13" s="243"/>
+      <c r="I13" s="254"/>
+      <c r="J13" s="256"/>
+      <c r="K13" s="257"/>
+      <c r="L13" s="259"/>
       <c r="M13" s="140" t="str">
         <f>RESUMEN!A20</f>
         <v>VTO 14/11</v>
@@ -6084,7 +6080,7 @@
         <v>90413.070804000003</v>
       </c>
       <c r="H14" s="44">
-        <f>G14</f>
+        <f t="shared" ref="H14:H20" si="0">G14</f>
         <v>90413.070804000003</v>
       </c>
       <c r="I14" s="159">
@@ -6095,24 +6091,24 @@
         <v>0</v>
       </c>
       <c r="K14" s="160">
-        <v>113901.49400400001</v>
-      </c>
-      <c r="L14" s="236">
+        <v>124701.49400400001</v>
+      </c>
+      <c r="L14" s="195">
         <v>0</v>
       </c>
       <c r="M14" s="161">
         <f>K14+J14+I14+L14</f>
-        <v>113901.49400400001</v>
+        <v>124701.49400400001</v>
       </c>
       <c r="N14" s="162">
         <f>M14*6% + M14</f>
-        <v>120735.58364424</v>
+        <v>132183.58364424002</v>
       </c>
       <c r="O14" s="121"/>
-      <c r="Q14" s="193" t="s">
+      <c r="Q14" s="248" t="s">
         <v>259</v>
       </c>
-      <c r="R14" s="193"/>
+      <c r="R14" s="248"/>
     </row>
     <row r="15" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A15" s="6"/>
@@ -6131,33 +6127,33 @@
         <v>107156.510912</v>
       </c>
       <c r="H15" s="44">
-        <f>G15</f>
+        <f t="shared" si="0"/>
         <v>107156.510912</v>
       </c>
       <c r="I15" s="159">
-        <f t="shared" ref="I15:I131" si="0">G15-H15</f>
+        <f t="shared" ref="I15:I131" si="1">G15-H15</f>
         <v>0</v>
       </c>
       <c r="J15" s="160">
         <v>0</v>
       </c>
       <c r="K15" s="160">
-        <v>134994.36326400004</v>
-      </c>
-      <c r="L15" s="236">
+        <v>147794.36326400004</v>
+      </c>
+      <c r="L15" s="195">
         <v>0</v>
       </c>
       <c r="M15" s="161">
-        <f t="shared" ref="M15:M18" si="1">K15+J15+I15+L15</f>
-        <v>134994.36326400004</v>
+        <f t="shared" ref="M15:M18" si="2">K15+J15+I15+L15</f>
+        <v>147794.36326400004</v>
       </c>
       <c r="N15" s="162">
-        <f t="shared" ref="N15:N18" si="2">M15*6% + M15</f>
-        <v>143094.02505984006</v>
+        <f t="shared" ref="N15:N18" si="3">M15*6% + M15</f>
+        <v>156662.02505984006</v>
       </c>
       <c r="O15" s="121"/>
-      <c r="Q15" s="193"/>
-      <c r="R15" s="193"/>
+      <c r="Q15" s="248"/>
+      <c r="R15" s="248"/>
     </row>
     <row r="16" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A16" s="6" t="s">
@@ -6178,29 +6174,29 @@
         <v>235861.50640899997</v>
       </c>
       <c r="H16" s="44">
-        <f>G16</f>
+        <f t="shared" si="0"/>
         <v>235861.50640899997</v>
       </c>
       <c r="I16" s="159">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="J16" s="160">
         <v>0</v>
       </c>
       <c r="K16" s="160">
-        <v>127611.859023</v>
-      </c>
-      <c r="L16" s="236">
+        <v>139711.859023</v>
+      </c>
+      <c r="L16" s="195">
         <v>0</v>
       </c>
       <c r="M16" s="161">
-        <f t="shared" si="1"/>
-        <v>127611.859023</v>
+        <f t="shared" si="2"/>
+        <v>139711.859023</v>
       </c>
       <c r="N16" s="162">
-        <f t="shared" si="2"/>
-        <v>135268.57056438</v>
+        <f t="shared" si="3"/>
+        <v>148094.57056438</v>
       </c>
       <c r="O16" s="121"/>
       <c r="Q16" t="s">
@@ -6208,7 +6204,7 @@
       </c>
       <c r="R16">
         <f>RESUMEN!F111</f>
-        <v>113901.49400400001</v>
+        <v>124701.49400400001</v>
       </c>
     </row>
     <row r="17" spans="1:18" x14ac:dyDescent="0.25">
@@ -6230,29 +6226,29 @@
         <v>307865.89588626003</v>
       </c>
       <c r="H17" s="44">
-        <f>G17</f>
+        <f t="shared" si="0"/>
         <v>307865.89588626003</v>
       </c>
       <c r="I17" s="159">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="J17" s="160">
         <v>0</v>
       </c>
       <c r="K17" s="160">
-        <v>157141.87598700004</v>
-      </c>
-      <c r="L17" s="236">
+        <v>172041.87598700004</v>
+      </c>
+      <c r="L17" s="195">
         <v>0</v>
       </c>
       <c r="M17" s="161">
-        <f t="shared" si="1"/>
-        <v>157141.87598700004</v>
+        <f t="shared" si="2"/>
+        <v>172041.87598700004</v>
       </c>
       <c r="N17" s="162">
-        <f t="shared" si="2"/>
-        <v>166570.38854622003</v>
+        <f t="shared" si="3"/>
+        <v>182364.38854622003</v>
       </c>
       <c r="O17" s="121"/>
       <c r="Q17" t="s">
@@ -6260,7 +6256,7 @@
       </c>
       <c r="R17">
         <f>RESUMEN!G111</f>
-        <v>134994.36326400004</v>
+        <v>147794.36326400004</v>
       </c>
     </row>
     <row r="18" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -6282,29 +6278,29 @@
         <v>145665.502962</v>
       </c>
       <c r="H18" s="167">
-        <f>G18</f>
+        <f t="shared" si="0"/>
         <v>145665.502962</v>
       </c>
       <c r="I18" s="168">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="J18" s="169">
         <v>0</v>
       </c>
       <c r="K18" s="169">
-        <v>183507.96256200003</v>
-      </c>
-      <c r="L18" s="236">
+        <v>200907.96256200003</v>
+      </c>
+      <c r="L18" s="195">
         <v>0</v>
       </c>
       <c r="M18" s="170">
-        <f t="shared" si="1"/>
-        <v>183507.96256200003</v>
+        <f t="shared" si="2"/>
+        <v>200907.96256200003</v>
       </c>
       <c r="N18" s="171">
-        <f t="shared" si="2"/>
-        <v>194518.44031572004</v>
+        <f t="shared" si="3"/>
+        <v>212962.44031572004</v>
       </c>
       <c r="O18" s="121"/>
       <c r="Q18" t="s">
@@ -6312,7 +6308,7 @@
       </c>
       <c r="R18">
         <f>RESUMEN!H111</f>
-        <v>127611.859023</v>
+        <v>139711.859023</v>
       </c>
     </row>
     <row r="19" spans="1:18" x14ac:dyDescent="0.25">
@@ -6334,7 +6330,7 @@
         <v>188000.01</v>
       </c>
       <c r="H19" s="174">
-        <f>G19</f>
+        <f t="shared" si="0"/>
         <v>188000.01</v>
       </c>
       <c r="I19" s="175">
@@ -6342,23 +6338,23 @@
         <v>0</v>
       </c>
       <c r="J19" s="176">
-        <f t="shared" ref="J19:J50" si="3">M$8*F19</f>
+        <f t="shared" ref="J19:J50" si="4">M$8*F19</f>
         <v>0</v>
       </c>
       <c r="K19" s="176">
         <f>M$2*F19</f>
-        <v>206800</v>
-      </c>
-      <c r="L19" s="236">
+        <v>225600</v>
+      </c>
+      <c r="L19" s="195">
         <v>0</v>
       </c>
       <c r="M19" s="177">
         <f>ROUND((K19+J19+I19+L19),0) + O19</f>
-        <v>206800.01</v>
+        <v>225600.01</v>
       </c>
       <c r="N19" s="177">
         <f>ROUND((M19*6% + M19 ),0) + O19</f>
-        <v>219208.01</v>
+        <v>239136.01</v>
       </c>
       <c r="O19" s="141">
         <v>0.01</v>
@@ -6368,7 +6364,7 @@
       </c>
       <c r="R19">
         <f>RESUMEN!I111</f>
-        <v>157141.87598700004</v>
+        <v>172041.87598700004</v>
       </c>
     </row>
     <row r="20" spans="1:18" x14ac:dyDescent="0.25">
@@ -6376,45 +6372,45 @@
         <v>124</v>
       </c>
       <c r="B20" s="6"/>
-      <c r="C20" s="254" t="s">
+      <c r="C20" s="207" t="s">
         <v>48</v>
       </c>
-      <c r="D20" s="255" t="s">
+      <c r="D20" s="208" t="s">
         <v>181</v>
       </c>
-      <c r="E20" s="256"/>
-      <c r="F20" s="257">
+      <c r="E20" s="209"/>
+      <c r="F20" s="210">
         <v>8.3999999999999995E-3</v>
       </c>
-      <c r="G20" s="258">
+      <c r="G20" s="211">
         <v>84000.02</v>
       </c>
-      <c r="H20" s="263">
-        <f>G20</f>
+      <c r="H20" s="216">
+        <f t="shared" si="0"/>
         <v>84000.02</v>
       </c>
-      <c r="I20" s="259">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="J20" s="260">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="K20" s="260">
-        <f t="shared" ref="K20:K50" si="4">M$2*F20</f>
-        <v>92400</v>
-      </c>
-      <c r="L20" s="261">
-        <v>0</v>
-      </c>
-      <c r="M20" s="262">
+      <c r="I20" s="212">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J20" s="213">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K20" s="213">
+        <f t="shared" ref="K20:K50" si="5">M$2*F20</f>
+        <v>100800</v>
+      </c>
+      <c r="L20" s="214">
+        <v>0</v>
+      </c>
+      <c r="M20" s="215">
         <f>ROUND((K20+J20+I20+L20),0) + O20</f>
-        <v>92400.02</v>
-      </c>
-      <c r="N20" s="262">
-        <f t="shared" ref="N20:N83" si="5">ROUND((M20*6% + M20 ),0) + O20</f>
-        <v>97944.02</v>
+        <v>100800.02</v>
+      </c>
+      <c r="N20" s="215">
+        <f t="shared" ref="N20:N83" si="6">ROUND((M20*6% + M20 ),0) + O20</f>
+        <v>106848.02</v>
       </c>
       <c r="O20" s="141">
         <f>O19+0.01</f>
@@ -6425,7 +6421,7 @@
       </c>
       <c r="R20">
         <f>RESUMEN!J111</f>
-        <v>183507.96256200003</v>
+        <v>200907.96256200003</v>
       </c>
     </row>
     <row r="21" spans="1:18" x14ac:dyDescent="0.25">
@@ -6451,30 +6447,30 @@
         <v>215099.09</v>
       </c>
       <c r="I21" s="159">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>-14099.059999999998</v>
       </c>
       <c r="J21" s="160">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="K21" s="160">
-        <f t="shared" si="4"/>
-        <v>221100</v>
-      </c>
-      <c r="L21" s="236">
+        <f t="shared" si="5"/>
+        <v>241200</v>
+      </c>
+      <c r="L21" s="195">
         <v>0</v>
       </c>
       <c r="M21" s="162">
-        <f t="shared" ref="M21:M83" si="6">ROUND((K21+J21+I21+L21),0) + O21</f>
-        <v>207001.03</v>
+        <f t="shared" ref="M21:M83" si="7">ROUND((K21+J21+I21+L21),0) + O21</f>
+        <v>227101.03</v>
       </c>
       <c r="N21" s="162">
-        <f t="shared" si="5"/>
-        <v>219421.03</v>
+        <f t="shared" si="6"/>
+        <v>240727.03</v>
       </c>
       <c r="O21" s="141">
-        <f t="shared" ref="O21:O84" si="7">O20+0.01</f>
+        <f t="shared" ref="O21:O84" si="8">O20+0.01</f>
         <v>0.03</v>
       </c>
     </row>
@@ -6483,49 +6479,49 @@
         <v>125</v>
       </c>
       <c r="B22" s="6"/>
-      <c r="C22" s="238" t="s">
+      <c r="C22" s="197" t="s">
         <v>50</v>
       </c>
-      <c r="D22" s="239" t="s">
+      <c r="D22" s="198" t="s">
         <v>183</v>
       </c>
-      <c r="E22" s="240" t="s">
+      <c r="E22" s="199" t="s">
         <v>304</v>
       </c>
-      <c r="F22" s="241">
+      <c r="F22" s="200">
         <v>9.4000000000000004E-3</v>
       </c>
-      <c r="G22" s="242">
+      <c r="G22" s="201">
         <v>259172.04</v>
       </c>
-      <c r="H22" s="270">
+      <c r="H22" s="220">
         <v>94000</v>
       </c>
-      <c r="I22" s="243">
-        <f t="shared" si="0"/>
+      <c r="I22" s="202">
+        <f t="shared" si="1"/>
         <v>165172.04</v>
       </c>
-      <c r="J22" s="244">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="K22" s="244">
+      <c r="J22" s="203">
         <f t="shared" si="4"/>
-        <v>103400</v>
-      </c>
-      <c r="L22" s="245">
-        <v>0</v>
-      </c>
-      <c r="M22" s="246">
+        <v>0</v>
+      </c>
+      <c r="K22" s="203">
+        <f t="shared" si="5"/>
+        <v>112800</v>
+      </c>
+      <c r="L22" s="204">
+        <v>0</v>
+      </c>
+      <c r="M22" s="205">
+        <f t="shared" si="7"/>
+        <v>277972.03999999998</v>
+      </c>
+      <c r="N22" s="205">
         <f t="shared" si="6"/>
-        <v>268572.03999999998</v>
-      </c>
-      <c r="N22" s="246">
-        <f t="shared" si="5"/>
-        <v>284686.03999999998</v>
+        <v>294650.03999999998</v>
       </c>
       <c r="O22" s="141">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0.04</v>
       </c>
       <c r="P22" t="s">
@@ -6554,30 +6550,30 @@
       </c>
       <c r="H23" s="44"/>
       <c r="I23" s="159">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>87000.05</v>
       </c>
       <c r="J23" s="160">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="K23" s="160">
-        <f t="shared" si="4"/>
-        <v>95700</v>
-      </c>
-      <c r="L23" s="236">
+        <f t="shared" si="5"/>
+        <v>104400</v>
+      </c>
+      <c r="L23" s="195">
         <v>0</v>
       </c>
       <c r="M23" s="162">
+        <f t="shared" si="7"/>
+        <v>191400.05</v>
+      </c>
+      <c r="N23" s="162">
         <f t="shared" si="6"/>
-        <v>182700.05</v>
-      </c>
-      <c r="N23" s="162">
-        <f t="shared" si="5"/>
-        <v>193662.05</v>
+        <v>202884.05</v>
       </c>
       <c r="O23" s="141">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0.05</v>
       </c>
     </row>
@@ -6602,34 +6598,34 @@
         <v>95000.06</v>
       </c>
       <c r="H24" s="44">
-        <f t="shared" ref="H24" si="8">G24</f>
+        <f t="shared" ref="H24" si="9">G24</f>
         <v>95000.06</v>
       </c>
       <c r="I24" s="159">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="J24" s="160">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="K24" s="160">
-        <f t="shared" si="4"/>
-        <v>104500</v>
-      </c>
-      <c r="L24" s="236">
+        <f t="shared" si="5"/>
+        <v>114000</v>
+      </c>
+      <c r="L24" s="195">
         <v>0</v>
       </c>
       <c r="M24" s="162">
+        <f t="shared" si="7"/>
+        <v>114000.06</v>
+      </c>
+      <c r="N24" s="162">
         <f t="shared" si="6"/>
-        <v>104500.06</v>
-      </c>
-      <c r="N24" s="162">
-        <f t="shared" si="5"/>
-        <v>110770.06</v>
+        <v>120840.06</v>
       </c>
       <c r="O24" s="141">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>6.0000000000000005E-2</v>
       </c>
     </row>
@@ -6657,30 +6653,30 @@
         <v>184976.07</v>
       </c>
       <c r="I25" s="159">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>102977</v>
       </c>
       <c r="J25" s="160">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="K25" s="160">
-        <f t="shared" si="4"/>
-        <v>181500</v>
-      </c>
-      <c r="L25" s="236">
+        <f t="shared" si="5"/>
+        <v>198000</v>
+      </c>
+      <c r="L25" s="195">
         <v>25000</v>
       </c>
       <c r="M25" s="162">
+        <f t="shared" si="7"/>
+        <v>325977.07</v>
+      </c>
+      <c r="N25" s="162">
         <f t="shared" si="6"/>
-        <v>309477.07</v>
-      </c>
-      <c r="N25" s="162">
-        <f t="shared" si="5"/>
-        <v>328046.07</v>
+        <v>345536.07</v>
       </c>
       <c r="O25" s="141">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
@@ -6689,48 +6685,48 @@
         <v>124</v>
       </c>
       <c r="B26" s="6"/>
-      <c r="C26" s="265" t="s">
+      <c r="C26" s="207" t="s">
         <v>54</v>
       </c>
-      <c r="D26" s="255" t="s">
+      <c r="D26" s="208" t="s">
         <v>275</v>
       </c>
-      <c r="E26" s="256"/>
-      <c r="F26" s="266">
+      <c r="E26" s="209"/>
+      <c r="F26" s="210">
         <v>7.3000000000000001E-3</v>
       </c>
-      <c r="G26" s="258">
+      <c r="G26" s="211">
         <v>73380.08</v>
       </c>
-      <c r="H26" s="263">
+      <c r="H26" s="216">
         <f>G26</f>
         <v>73380.08</v>
       </c>
-      <c r="I26" s="259">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="J26" s="260">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="K26" s="260">
+      <c r="I26" s="212">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J26" s="213">
         <f t="shared" si="4"/>
-        <v>80300</v>
-      </c>
-      <c r="L26" s="261">
-        <v>0</v>
-      </c>
-      <c r="M26" s="267">
+        <v>0</v>
+      </c>
+      <c r="K26" s="213">
+        <f t="shared" si="5"/>
+        <v>87600</v>
+      </c>
+      <c r="L26" s="214">
+        <v>0</v>
+      </c>
+      <c r="M26" s="215">
+        <f t="shared" si="7"/>
+        <v>87600.08</v>
+      </c>
+      <c r="N26" s="215">
         <f t="shared" si="6"/>
-        <v>80300.08</v>
-      </c>
-      <c r="N26" s="267">
-        <f t="shared" si="5"/>
-        <v>85118.080000000002</v>
+        <v>92856.08</v>
       </c>
       <c r="O26" s="141">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0.08</v>
       </c>
     </row>
@@ -6754,30 +6750,30 @@
       </c>
       <c r="H27" s="44"/>
       <c r="I27" s="159">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>490772.09</v>
       </c>
       <c r="J27" s="160">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="K27" s="160">
-        <f t="shared" si="4"/>
-        <v>195800</v>
-      </c>
-      <c r="L27" s="236">
+        <f t="shared" si="5"/>
+        <v>213600</v>
+      </c>
+      <c r="L27" s="195">
         <v>24000</v>
       </c>
       <c r="M27" s="162">
+        <f t="shared" si="7"/>
+        <v>728372.09</v>
+      </c>
+      <c r="N27" s="162">
         <f t="shared" si="6"/>
-        <v>710572.09</v>
-      </c>
-      <c r="N27" s="162">
-        <f t="shared" si="5"/>
-        <v>753206.09</v>
+        <v>772074.09</v>
       </c>
       <c r="O27" s="141">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0.09</v>
       </c>
     </row>
@@ -6803,30 +6799,30 @@
         <v>278992.09999999998</v>
       </c>
       <c r="I28" s="159">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="J28" s="160">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="K28" s="160">
-        <f t="shared" si="4"/>
-        <v>103400</v>
-      </c>
-      <c r="L28" s="236">
+        <f t="shared" si="5"/>
+        <v>112800</v>
+      </c>
+      <c r="L28" s="195">
         <v>0</v>
       </c>
       <c r="M28" s="162">
+        <f t="shared" si="7"/>
+        <v>112800.1</v>
+      </c>
+      <c r="N28" s="162">
         <f t="shared" si="6"/>
-        <v>103400.1</v>
-      </c>
-      <c r="N28" s="162">
-        <f t="shared" si="5"/>
-        <v>109604.1</v>
+        <v>119568.1</v>
       </c>
       <c r="O28" s="141">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>9.9999999999999992E-2</v>
       </c>
     </row>
@@ -6835,47 +6831,47 @@
         <v>125</v>
       </c>
       <c r="B29" s="6"/>
-      <c r="C29" s="254" t="s">
+      <c r="C29" s="207" t="s">
         <v>57</v>
       </c>
-      <c r="D29" s="255" t="s">
+      <c r="D29" s="208" t="s">
         <v>303</v>
       </c>
-      <c r="E29" s="256"/>
-      <c r="F29" s="257">
+      <c r="E29" s="209"/>
+      <c r="F29" s="210">
         <v>8.6999999999999994E-3</v>
       </c>
-      <c r="G29" s="258">
+      <c r="G29" s="211">
         <v>77604.11</v>
       </c>
-      <c r="H29" s="263">
+      <c r="H29" s="216">
         <v>82260.11</v>
       </c>
-      <c r="I29" s="259">
-        <f t="shared" si="0"/>
+      <c r="I29" s="212">
+        <f t="shared" si="1"/>
         <v>-4656</v>
       </c>
-      <c r="J29" s="260">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="K29" s="260">
+      <c r="J29" s="213">
         <f t="shared" si="4"/>
-        <v>95700</v>
-      </c>
-      <c r="L29" s="261">
-        <v>0</v>
-      </c>
-      <c r="M29" s="262">
+        <v>0</v>
+      </c>
+      <c r="K29" s="213">
+        <f t="shared" si="5"/>
+        <v>104400</v>
+      </c>
+      <c r="L29" s="214">
+        <v>0</v>
+      </c>
+      <c r="M29" s="215">
+        <f t="shared" si="7"/>
+        <v>99744.11</v>
+      </c>
+      <c r="N29" s="215">
         <f t="shared" si="6"/>
-        <v>91044.11</v>
-      </c>
-      <c r="N29" s="262">
-        <f t="shared" si="5"/>
-        <v>96507.11</v>
+        <v>105729.11</v>
       </c>
       <c r="O29" s="141">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0.10999999999999999</v>
       </c>
     </row>
@@ -6899,30 +6895,30 @@
       </c>
       <c r="H30" s="44"/>
       <c r="I30" s="159">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>266000.12</v>
       </c>
       <c r="J30" s="160">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="K30" s="160">
-        <f t="shared" si="4"/>
-        <v>104500</v>
-      </c>
-      <c r="L30" s="236">
+        <f t="shared" si="5"/>
+        <v>114000</v>
+      </c>
+      <c r="L30" s="195">
         <v>0</v>
       </c>
       <c r="M30" s="162">
+        <f t="shared" si="7"/>
+        <v>380000.12</v>
+      </c>
+      <c r="N30" s="162">
         <f t="shared" si="6"/>
-        <v>370500.12</v>
-      </c>
-      <c r="N30" s="162">
-        <f t="shared" si="5"/>
-        <v>392730.12</v>
+        <v>402800.12</v>
       </c>
       <c r="O30" s="141">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0.11999999999999998</v>
       </c>
     </row>
@@ -6949,30 +6945,30 @@
         <v>164000.13</v>
       </c>
       <c r="I31" s="159">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="J31" s="160">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="K31" s="160">
-        <f t="shared" si="4"/>
-        <v>180400.00000000003</v>
-      </c>
-      <c r="L31" s="236">
+        <f t="shared" si="5"/>
+        <v>196800.00000000003</v>
+      </c>
+      <c r="L31" s="195">
         <v>0</v>
       </c>
       <c r="M31" s="162">
+        <f t="shared" si="7"/>
+        <v>196800.13</v>
+      </c>
+      <c r="N31" s="162">
         <f t="shared" si="6"/>
-        <v>180400.13</v>
-      </c>
-      <c r="N31" s="162">
-        <f t="shared" si="5"/>
-        <v>191224.13</v>
+        <v>208608.13</v>
       </c>
       <c r="O31" s="141">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0.12999999999999998</v>
       </c>
     </row>
@@ -7001,30 +6997,30 @@
         <v>72000.14</v>
       </c>
       <c r="I32" s="159">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="J32" s="160">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="K32" s="160">
-        <f t="shared" si="4"/>
-        <v>79200</v>
-      </c>
-      <c r="L32" s="236">
+        <f t="shared" si="5"/>
+        <v>86400</v>
+      </c>
+      <c r="L32" s="195">
         <v>0</v>
       </c>
       <c r="M32" s="162">
+        <f t="shared" si="7"/>
+        <v>86400.14</v>
+      </c>
+      <c r="N32" s="162">
         <f t="shared" si="6"/>
-        <v>79200.14</v>
-      </c>
-      <c r="N32" s="162">
-        <f t="shared" si="5"/>
-        <v>83952.14</v>
+        <v>91584.14</v>
       </c>
       <c r="O32" s="141">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0.13999999999999999</v>
       </c>
     </row>
@@ -7051,30 +7047,30 @@
         <v>173000.15</v>
       </c>
       <c r="I33" s="178">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="J33" s="160">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="K33" s="160">
-        <f t="shared" si="4"/>
-        <v>190300</v>
-      </c>
-      <c r="L33" s="236">
+        <f t="shared" si="5"/>
+        <v>207600</v>
+      </c>
+      <c r="L33" s="195">
         <v>0</v>
       </c>
       <c r="M33" s="162">
+        <f t="shared" si="7"/>
+        <v>207600.15</v>
+      </c>
+      <c r="N33" s="162">
         <f t="shared" si="6"/>
-        <v>190300.15</v>
-      </c>
-      <c r="N33" s="162">
-        <f t="shared" si="5"/>
-        <v>201718.15</v>
+        <v>220056.15</v>
       </c>
       <c r="O33" s="141">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0.15</v>
       </c>
     </row>
@@ -7101,30 +7097,30 @@
         <v>94000.16</v>
       </c>
       <c r="I34" s="159">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="J34" s="160">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="K34" s="160">
-        <f t="shared" si="4"/>
-        <v>103400</v>
-      </c>
-      <c r="L34" s="236">
+        <f t="shared" si="5"/>
+        <v>112800</v>
+      </c>
+      <c r="L34" s="195">
         <v>12000</v>
       </c>
       <c r="M34" s="162">
+        <f t="shared" si="7"/>
+        <v>124800.16</v>
+      </c>
+      <c r="N34" s="162">
         <f t="shared" si="6"/>
-        <v>115400.16</v>
-      </c>
-      <c r="N34" s="162">
-        <f t="shared" si="5"/>
-        <v>122324.16</v>
+        <v>132288.16</v>
       </c>
       <c r="O34" s="141">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0.16</v>
       </c>
     </row>
@@ -7152,30 +7148,30 @@
         <v>78300.17</v>
       </c>
       <c r="I35" s="159">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>17400</v>
       </c>
       <c r="J35" s="160">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="K35" s="160">
-        <f t="shared" si="4"/>
-        <v>95700</v>
-      </c>
-      <c r="L35" s="236">
+        <f t="shared" si="5"/>
+        <v>104400</v>
+      </c>
+      <c r="L35" s="195">
         <v>0</v>
       </c>
       <c r="M35" s="162">
+        <f t="shared" si="7"/>
+        <v>121800.17</v>
+      </c>
+      <c r="N35" s="162">
         <f t="shared" si="6"/>
-        <v>113100.17</v>
-      </c>
-      <c r="N35" s="162">
-        <f t="shared" si="5"/>
-        <v>119886.17</v>
+        <v>129108.17</v>
       </c>
       <c r="O35" s="141">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0.17</v>
       </c>
     </row>
@@ -7199,30 +7195,30 @@
       </c>
       <c r="H36" s="44"/>
       <c r="I36" s="178">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>95000.18</v>
       </c>
       <c r="J36" s="160">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="K36" s="160">
-        <f t="shared" si="4"/>
-        <v>104500</v>
-      </c>
-      <c r="L36" s="236">
+        <f t="shared" si="5"/>
+        <v>114000</v>
+      </c>
+      <c r="L36" s="195">
         <v>0</v>
       </c>
       <c r="M36" s="162">
+        <f t="shared" si="7"/>
+        <v>209000.18</v>
+      </c>
+      <c r="N36" s="162">
         <f t="shared" si="6"/>
-        <v>199500.18</v>
-      </c>
-      <c r="N36" s="162">
-        <f t="shared" si="5"/>
-        <v>211470.18</v>
+        <v>221540.18</v>
       </c>
       <c r="O36" s="141">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0.18000000000000002</v>
       </c>
     </row>
@@ -7251,31 +7247,31 @@
         <v>164000.19</v>
       </c>
       <c r="I37" s="159">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="J37" s="160">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="K37" s="160">
-        <f t="shared" si="4"/>
-        <v>180400.00000000003</v>
-      </c>
-      <c r="L37" s="236">
+        <f t="shared" si="5"/>
+        <v>196800.00000000003</v>
+      </c>
+      <c r="L37" s="195">
         <f>12000+25000</f>
         <v>37000</v>
       </c>
       <c r="M37" s="162">
+        <f t="shared" si="7"/>
+        <v>233800.19</v>
+      </c>
+      <c r="N37" s="162">
         <f t="shared" si="6"/>
-        <v>217400.19</v>
-      </c>
-      <c r="N37" s="162">
-        <f t="shared" si="5"/>
-        <v>230444.19</v>
+        <v>247828.19</v>
       </c>
       <c r="O37" s="141">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0.19000000000000003</v>
       </c>
     </row>
@@ -7284,48 +7280,48 @@
         <v>124</v>
       </c>
       <c r="B38" s="6"/>
-      <c r="C38" s="254" t="s">
+      <c r="C38" s="207" t="s">
         <v>66</v>
       </c>
-      <c r="D38" s="255" t="s">
+      <c r="D38" s="208" t="s">
         <v>225</v>
       </c>
-      <c r="E38" s="256"/>
-      <c r="F38" s="257">
+      <c r="E38" s="209"/>
+      <c r="F38" s="210">
         <v>7.1999999999999998E-3</v>
       </c>
-      <c r="G38" s="258">
+      <c r="G38" s="211">
         <v>72000.2</v>
       </c>
-      <c r="H38" s="263">
+      <c r="H38" s="216">
         <f>G38</f>
         <v>72000.2</v>
       </c>
-      <c r="I38" s="259">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="J38" s="260">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="K38" s="260">
+      <c r="I38" s="212">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J38" s="213">
         <f t="shared" si="4"/>
-        <v>79200</v>
-      </c>
-      <c r="L38" s="261">
-        <v>0</v>
-      </c>
-      <c r="M38" s="262">
+        <v>0</v>
+      </c>
+      <c r="K38" s="213">
+        <f t="shared" si="5"/>
+        <v>86400</v>
+      </c>
+      <c r="L38" s="214">
+        <v>0</v>
+      </c>
+      <c r="M38" s="215">
+        <f t="shared" si="7"/>
+        <v>86400.2</v>
+      </c>
+      <c r="N38" s="215">
         <f t="shared" si="6"/>
-        <v>79200.2</v>
-      </c>
-      <c r="N38" s="262">
-        <f t="shared" si="5"/>
-        <v>83952.2</v>
+        <v>91584.2</v>
       </c>
       <c r="O38" s="141">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0.20000000000000004</v>
       </c>
     </row>
@@ -7352,30 +7348,30 @@
         <v>644445.21</v>
       </c>
       <c r="I39" s="159">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="J39" s="160">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="K39" s="160">
-        <f t="shared" si="4"/>
-        <v>190300</v>
-      </c>
-      <c r="L39" s="236">
+        <f t="shared" si="5"/>
+        <v>207600</v>
+      </c>
+      <c r="L39" s="195">
         <v>0</v>
       </c>
       <c r="M39" s="162">
+        <f t="shared" si="7"/>
+        <v>207600.21</v>
+      </c>
+      <c r="N39" s="162">
         <f t="shared" si="6"/>
-        <v>190300.21</v>
-      </c>
-      <c r="N39" s="162">
-        <f t="shared" si="5"/>
-        <v>201718.21</v>
-      </c>
-      <c r="O39" s="268">
-        <f t="shared" si="7"/>
+        <v>220056.21</v>
+      </c>
+      <c r="O39" s="218">
+        <f t="shared" si="8"/>
         <v>0.21000000000000005</v>
       </c>
       <c r="P39" s="74"/>
@@ -7497,30 +7493,30 @@
       </c>
       <c r="H40" s="44"/>
       <c r="I40" s="159">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>94000.22</v>
       </c>
       <c r="J40" s="160">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="K40" s="160">
-        <f t="shared" si="4"/>
-        <v>103400</v>
-      </c>
-      <c r="L40" s="236">
+        <f t="shared" si="5"/>
+        <v>112800</v>
+      </c>
+      <c r="L40" s="195">
         <v>0</v>
       </c>
       <c r="M40" s="162">
+        <f t="shared" si="7"/>
+        <v>206800.22</v>
+      </c>
+      <c r="N40" s="162">
         <f t="shared" si="6"/>
-        <v>197400.22</v>
-      </c>
-      <c r="N40" s="162">
-        <f t="shared" si="5"/>
-        <v>209244.22</v>
-      </c>
-      <c r="O40" s="268">
-        <f t="shared" si="7"/>
+        <v>219208.22</v>
+      </c>
+      <c r="O40" s="218">
+        <f t="shared" si="8"/>
         <v>0.22000000000000006</v>
       </c>
       <c r="P40" s="74"/>
@@ -7627,48 +7623,48 @@
         <v>125</v>
       </c>
       <c r="B41" s="149"/>
-      <c r="C41" s="254" t="s">
+      <c r="C41" s="207" t="s">
         <v>69</v>
       </c>
-      <c r="D41" s="255" t="s">
+      <c r="D41" s="208" t="s">
         <v>186</v>
       </c>
-      <c r="E41" s="256"/>
-      <c r="F41" s="257">
+      <c r="E41" s="209"/>
+      <c r="F41" s="210">
         <v>8.6999999999999994E-3</v>
       </c>
-      <c r="G41" s="258">
+      <c r="G41" s="211">
         <v>87000.23</v>
       </c>
-      <c r="H41" s="263">
+      <c r="H41" s="216">
         <f>G41</f>
         <v>87000.23</v>
       </c>
-      <c r="I41" s="259">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="J41" s="260">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="K41" s="260">
+      <c r="I41" s="212">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J41" s="213">
         <f t="shared" si="4"/>
-        <v>95700</v>
-      </c>
-      <c r="L41" s="261">
-        <v>0</v>
-      </c>
-      <c r="M41" s="262">
+        <v>0</v>
+      </c>
+      <c r="K41" s="213">
+        <f t="shared" si="5"/>
+        <v>104400</v>
+      </c>
+      <c r="L41" s="214">
+        <v>0</v>
+      </c>
+      <c r="M41" s="215">
+        <f t="shared" si="7"/>
+        <v>104400.23</v>
+      </c>
+      <c r="N41" s="215">
         <f t="shared" si="6"/>
-        <v>95700.23</v>
-      </c>
-      <c r="N41" s="262">
-        <f t="shared" si="5"/>
-        <v>101442.23</v>
-      </c>
-      <c r="O41" s="268">
-        <f t="shared" si="7"/>
+        <v>110664.23</v>
+      </c>
+      <c r="O41" s="218">
+        <f t="shared" si="8"/>
         <v>0.23000000000000007</v>
       </c>
       <c r="P41" s="74" t="s">
@@ -7792,30 +7788,30 @@
       </c>
       <c r="H42" s="44"/>
       <c r="I42" s="159">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>95000.24</v>
       </c>
       <c r="J42" s="160">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="K42" s="160">
-        <f t="shared" si="4"/>
-        <v>104500</v>
-      </c>
-      <c r="L42" s="236">
+        <f t="shared" si="5"/>
+        <v>114000</v>
+      </c>
+      <c r="L42" s="195">
         <v>0</v>
       </c>
       <c r="M42" s="162">
+        <f t="shared" si="7"/>
+        <v>209000.24</v>
+      </c>
+      <c r="N42" s="162">
         <f t="shared" si="6"/>
-        <v>199500.24</v>
-      </c>
-      <c r="N42" s="162">
-        <f t="shared" si="5"/>
-        <v>211470.24</v>
-      </c>
-      <c r="O42" s="268">
-        <f t="shared" si="7"/>
+        <v>221540.24</v>
+      </c>
+      <c r="O42" s="218">
+        <f t="shared" si="8"/>
         <v>0.24000000000000007</v>
       </c>
       <c r="P42" s="74"/>
@@ -7940,30 +7936,30 @@
         <v>164000.25</v>
       </c>
       <c r="I43" s="159">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="J43" s="160">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="K43" s="160">
-        <f t="shared" si="4"/>
-        <v>180400.00000000003</v>
-      </c>
-      <c r="L43" s="236">
+        <f t="shared" si="5"/>
+        <v>196800.00000000003</v>
+      </c>
+      <c r="L43" s="195">
         <v>0</v>
       </c>
       <c r="M43" s="162">
+        <f t="shared" si="7"/>
+        <v>196800.25</v>
+      </c>
+      <c r="N43" s="162">
         <f t="shared" si="6"/>
-        <v>180400.25</v>
-      </c>
-      <c r="N43" s="162">
-        <f t="shared" si="5"/>
-        <v>191224.25</v>
+        <v>208608.25</v>
       </c>
       <c r="O43" s="141">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0.25000000000000006</v>
       </c>
     </row>
@@ -7992,30 +7988,30 @@
         <v>72000.259999999995</v>
       </c>
       <c r="I44" s="159">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="J44" s="160">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="K44" s="160">
-        <f t="shared" si="4"/>
-        <v>79200</v>
-      </c>
-      <c r="L44" s="236">
+        <f t="shared" si="5"/>
+        <v>86400</v>
+      </c>
+      <c r="L44" s="195">
         <v>0</v>
       </c>
       <c r="M44" s="162">
+        <f t="shared" si="7"/>
+        <v>86400.26</v>
+      </c>
+      <c r="N44" s="162">
         <f t="shared" si="6"/>
-        <v>79200.259999999995</v>
-      </c>
-      <c r="N44" s="162">
-        <f t="shared" si="5"/>
-        <v>83952.26</v>
+        <v>91584.26</v>
       </c>
       <c r="O44" s="141">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0.26000000000000006</v>
       </c>
     </row>
@@ -8038,34 +8034,34 @@
         <v>173000.27</v>
       </c>
       <c r="H45" s="44">
-        <f t="shared" ref="H45:H51" si="9">G45</f>
+        <f t="shared" ref="H45:H51" si="10">G45</f>
         <v>173000.27</v>
       </c>
       <c r="I45" s="159">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="J45" s="160">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="K45" s="160">
-        <f t="shared" si="4"/>
-        <v>190300</v>
-      </c>
-      <c r="L45" s="236">
+        <f t="shared" si="5"/>
+        <v>207600</v>
+      </c>
+      <c r="L45" s="195">
         <v>0</v>
       </c>
       <c r="M45" s="162">
+        <f t="shared" si="7"/>
+        <v>207600.27</v>
+      </c>
+      <c r="N45" s="162">
         <f t="shared" si="6"/>
-        <v>190300.27</v>
-      </c>
-      <c r="N45" s="162">
-        <f t="shared" si="5"/>
-        <v>201718.27</v>
+        <v>220056.27</v>
       </c>
       <c r="O45" s="141">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0.27000000000000007</v>
       </c>
       <c r="P45" t="s">
@@ -8080,48 +8076,48 @@
         <v>125</v>
       </c>
       <c r="B46" s="6"/>
-      <c r="C46" s="254" t="s">
+      <c r="C46" s="207" t="s">
         <v>74</v>
       </c>
-      <c r="D46" s="255" t="s">
+      <c r="D46" s="208" t="s">
         <v>122</v>
       </c>
-      <c r="E46" s="256"/>
-      <c r="F46" s="257">
+      <c r="E46" s="209"/>
+      <c r="F46" s="210">
         <v>9.4000000000000004E-3</v>
       </c>
-      <c r="G46" s="258">
+      <c r="G46" s="211">
         <v>94000.28</v>
       </c>
-      <c r="H46" s="263">
-        <f t="shared" si="9"/>
+      <c r="H46" s="216">
+        <f t="shared" si="10"/>
         <v>94000.28</v>
       </c>
-      <c r="I46" s="259">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="J46" s="260">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="K46" s="260">
+      <c r="I46" s="212">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J46" s="213">
         <f t="shared" si="4"/>
-        <v>103400</v>
-      </c>
-      <c r="L46" s="261">
-        <v>0</v>
-      </c>
-      <c r="M46" s="262">
+        <v>0</v>
+      </c>
+      <c r="K46" s="213">
+        <f t="shared" si="5"/>
+        <v>112800</v>
+      </c>
+      <c r="L46" s="214">
+        <v>0</v>
+      </c>
+      <c r="M46" s="215">
+        <f t="shared" si="7"/>
+        <v>112800.28</v>
+      </c>
+      <c r="N46" s="215">
         <f t="shared" si="6"/>
-        <v>103400.28</v>
-      </c>
-      <c r="N46" s="262">
-        <f t="shared" si="5"/>
-        <v>109604.28</v>
+        <v>119568.28</v>
       </c>
       <c r="O46" s="141">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0.28000000000000008</v>
       </c>
       <c r="Q46" t="s">
@@ -8149,34 +8145,34 @@
         <v>87000.29</v>
       </c>
       <c r="H47" s="44">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>87000.29</v>
       </c>
       <c r="I47" s="159">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="J47" s="160">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="K47" s="160">
-        <f t="shared" si="4"/>
-        <v>95700</v>
-      </c>
-      <c r="L47" s="236">
+        <f t="shared" si="5"/>
+        <v>104400</v>
+      </c>
+      <c r="L47" s="195">
         <v>0</v>
       </c>
       <c r="M47" s="162">
+        <f t="shared" si="7"/>
+        <v>104400.29</v>
+      </c>
+      <c r="N47" s="162">
         <f t="shared" si="6"/>
-        <v>95700.29</v>
-      </c>
-      <c r="N47" s="162">
-        <f t="shared" si="5"/>
-        <v>101442.29</v>
+        <v>110664.29</v>
       </c>
       <c r="O47" s="141">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0.29000000000000009</v>
       </c>
     </row>
@@ -8199,34 +8195,34 @@
         <v>95000.3</v>
       </c>
       <c r="H48" s="44">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>95000.3</v>
       </c>
       <c r="I48" s="159">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="J48" s="160">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="K48" s="160">
-        <f t="shared" si="4"/>
-        <v>104500</v>
-      </c>
-      <c r="L48" s="236">
+        <f t="shared" si="5"/>
+        <v>114000</v>
+      </c>
+      <c r="L48" s="195">
         <v>0</v>
       </c>
       <c r="M48" s="162">
+        <f t="shared" si="7"/>
+        <v>114000.3</v>
+      </c>
+      <c r="N48" s="162">
         <f t="shared" si="6"/>
-        <v>104500.3</v>
-      </c>
-      <c r="N48" s="162">
-        <f t="shared" si="5"/>
-        <v>110770.3</v>
+        <v>120840.3</v>
       </c>
       <c r="O48" s="141">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0.3000000000000001</v>
       </c>
     </row>
@@ -8249,34 +8245,34 @@
         <v>164000.31</v>
       </c>
       <c r="H49" s="44">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>164000.31</v>
       </c>
       <c r="I49" s="159">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="J49" s="160">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="K49" s="160">
-        <f t="shared" si="4"/>
-        <v>180400.00000000003</v>
-      </c>
-      <c r="L49" s="236">
+        <f t="shared" si="5"/>
+        <v>196800.00000000003</v>
+      </c>
+      <c r="L49" s="195">
         <v>0</v>
       </c>
       <c r="M49" s="162">
+        <f t="shared" si="7"/>
+        <v>196800.31</v>
+      </c>
+      <c r="N49" s="162">
         <f t="shared" si="6"/>
-        <v>180400.31</v>
-      </c>
-      <c r="N49" s="162">
-        <f t="shared" si="5"/>
-        <v>191224.31</v>
+        <v>208608.31</v>
       </c>
       <c r="O49" s="141">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0.31000000000000011</v>
       </c>
     </row>
@@ -8299,34 +8295,34 @@
         <v>72000.320000000007</v>
       </c>
       <c r="H50" s="44">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>72000.320000000007</v>
       </c>
       <c r="I50" s="159">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="J50" s="160">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="K50" s="160">
-        <f t="shared" si="4"/>
-        <v>79200</v>
-      </c>
-      <c r="L50" s="236">
+        <f t="shared" si="5"/>
+        <v>86400</v>
+      </c>
+      <c r="L50" s="195">
         <v>0</v>
       </c>
       <c r="M50" s="162">
+        <f t="shared" si="7"/>
+        <v>86400.320000000007</v>
+      </c>
+      <c r="N50" s="162">
         <f t="shared" si="6"/>
-        <v>79200.320000000007</v>
-      </c>
-      <c r="N50" s="162">
-        <f t="shared" si="5"/>
-        <v>83952.320000000007</v>
+        <v>91584.320000000007</v>
       </c>
       <c r="O50" s="141">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0.32000000000000012</v>
       </c>
       <c r="P50" s="43"/>
@@ -8336,48 +8332,48 @@
         <v>123</v>
       </c>
       <c r="B51" s="6"/>
-      <c r="C51" s="254" t="s">
+      <c r="C51" s="207" t="s">
         <v>79</v>
       </c>
-      <c r="D51" s="255" t="s">
+      <c r="D51" s="208" t="s">
         <v>197</v>
       </c>
-      <c r="E51" s="256"/>
-      <c r="F51" s="257">
+      <c r="E51" s="209"/>
+      <c r="F51" s="210">
         <v>1.7299999999999999E-2</v>
       </c>
-      <c r="G51" s="258">
+      <c r="G51" s="211">
         <v>173000.33</v>
       </c>
-      <c r="H51" s="263">
-        <f t="shared" si="9"/>
+      <c r="H51" s="216">
+        <f t="shared" si="10"/>
         <v>173000.33</v>
       </c>
-      <c r="I51" s="259">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="J51" s="260">
-        <f t="shared" ref="J51:J82" si="10">M$8*F51</f>
-        <v>0</v>
-      </c>
-      <c r="K51" s="260">
-        <f t="shared" ref="K51:K82" si="11">M$2*F51</f>
-        <v>190300</v>
-      </c>
-      <c r="L51" s="261">
-        <v>0</v>
-      </c>
-      <c r="M51" s="262">
+      <c r="I51" s="212">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J51" s="213">
+        <f t="shared" ref="J51:J82" si="11">M$8*F51</f>
+        <v>0</v>
+      </c>
+      <c r="K51" s="213">
+        <f t="shared" ref="K51:K82" si="12">M$2*F51</f>
+        <v>207600</v>
+      </c>
+      <c r="L51" s="214">
+        <v>0</v>
+      </c>
+      <c r="M51" s="215">
+        <f t="shared" si="7"/>
+        <v>207600.33</v>
+      </c>
+      <c r="N51" s="215">
         <f t="shared" si="6"/>
-        <v>190300.33</v>
-      </c>
-      <c r="N51" s="262">
-        <f t="shared" si="5"/>
-        <v>201718.33</v>
+        <v>220056.33</v>
       </c>
       <c r="O51" s="141">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0.33000000000000013</v>
       </c>
       <c r="P51" s="43"/>
@@ -8405,30 +8401,30 @@
         <v>93999.34</v>
       </c>
       <c r="I52" s="159">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="J52" s="160">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="K52" s="160">
-        <f t="shared" si="11"/>
-        <v>103400</v>
-      </c>
-      <c r="L52" s="236">
+        <f t="shared" si="12"/>
+        <v>112800</v>
+      </c>
+      <c r="L52" s="195">
         <v>12000</v>
       </c>
       <c r="M52" s="162">
+        <f t="shared" si="7"/>
+        <v>124800.34</v>
+      </c>
+      <c r="N52" s="162">
         <f t="shared" si="6"/>
-        <v>115400.34</v>
-      </c>
-      <c r="N52" s="162">
-        <f t="shared" si="5"/>
-        <v>122324.34</v>
+        <v>132288.34</v>
       </c>
       <c r="O52" s="141">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0.34000000000000014</v>
       </c>
       <c r="P52" t="s">
@@ -8461,26 +8457,26 @@
         <v>8700</v>
       </c>
       <c r="J53" s="160">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="K53" s="160">
-        <f t="shared" si="11"/>
-        <v>95700</v>
-      </c>
-      <c r="L53" s="236">
+        <f t="shared" si="12"/>
+        <v>104400</v>
+      </c>
+      <c r="L53" s="195">
         <v>0</v>
       </c>
       <c r="M53" s="162">
+        <f t="shared" si="7"/>
+        <v>113100.35</v>
+      </c>
+      <c r="N53" s="162">
         <f t="shared" si="6"/>
-        <v>104400.35</v>
-      </c>
-      <c r="N53" s="162">
-        <f t="shared" si="5"/>
-        <v>110664.35</v>
+        <v>119886.35</v>
       </c>
       <c r="O53" s="141">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0.35000000000000014</v>
       </c>
     </row>
@@ -8503,7 +8499,7 @@
         <v>95000.36</v>
       </c>
       <c r="H54" s="44">
-        <f t="shared" ref="H54:H59" si="12">G54</f>
+        <f t="shared" ref="H54:H57" si="13">G54</f>
         <v>95000.36</v>
       </c>
       <c r="I54" s="159">
@@ -8511,26 +8507,26 @@
         <v>0</v>
       </c>
       <c r="J54" s="160">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="K54" s="160">
-        <f t="shared" si="11"/>
-        <v>104500</v>
-      </c>
-      <c r="L54" s="236">
+        <f t="shared" si="12"/>
+        <v>114000</v>
+      </c>
+      <c r="L54" s="195">
         <v>36000</v>
       </c>
       <c r="M54" s="162">
+        <f t="shared" si="7"/>
+        <v>150000.35999999999</v>
+      </c>
+      <c r="N54" s="162">
         <f t="shared" si="6"/>
-        <v>140500.35999999999</v>
-      </c>
-      <c r="N54" s="162">
-        <f t="shared" si="5"/>
-        <v>148930.35999999999</v>
+        <v>159000.35999999999</v>
       </c>
       <c r="O54" s="141">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0.36000000000000015</v>
       </c>
     </row>
@@ -8553,34 +8549,34 @@
         <v>164000.37</v>
       </c>
       <c r="H55" s="44">
+        <f t="shared" si="13"/>
+        <v>164000.37</v>
+      </c>
+      <c r="I55" s="159">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J55" s="160">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="K55" s="160">
         <f t="shared" si="12"/>
-        <v>164000.37</v>
-      </c>
-      <c r="I55" s="159">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="J55" s="160">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="K55" s="160">
-        <f t="shared" si="11"/>
-        <v>180400.00000000003</v>
-      </c>
-      <c r="L55" s="236">
+        <v>196800.00000000003</v>
+      </c>
+      <c r="L55" s="195">
         <v>0</v>
       </c>
       <c r="M55" s="162">
+        <f t="shared" si="7"/>
+        <v>196800.37</v>
+      </c>
+      <c r="N55" s="162">
         <f t="shared" si="6"/>
-        <v>180400.37</v>
-      </c>
-      <c r="N55" s="162">
-        <f t="shared" si="5"/>
-        <v>191224.37</v>
+        <v>208608.37</v>
       </c>
       <c r="O55" s="141">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0.37000000000000016</v>
       </c>
       <c r="Q55" s="59"/>
@@ -8606,34 +8602,34 @@
         <v>72000.38</v>
       </c>
       <c r="H56" s="44">
+        <f t="shared" si="13"/>
+        <v>72000.38</v>
+      </c>
+      <c r="I56" s="159">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J56" s="160">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="K56" s="160">
         <f t="shared" si="12"/>
-        <v>72000.38</v>
-      </c>
-      <c r="I56" s="159">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="J56" s="160">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="K56" s="160">
-        <f t="shared" si="11"/>
-        <v>79200</v>
-      </c>
-      <c r="L56" s="236">
+        <v>86400</v>
+      </c>
+      <c r="L56" s="195">
         <v>0</v>
       </c>
       <c r="M56" s="162">
+        <f t="shared" si="7"/>
+        <v>86400.38</v>
+      </c>
+      <c r="N56" s="162">
         <f t="shared" si="6"/>
-        <v>79200.38</v>
-      </c>
-      <c r="N56" s="162">
-        <f t="shared" si="5"/>
-        <v>83952.38</v>
+        <v>91584.38</v>
       </c>
       <c r="O56" s="141">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0.38000000000000017</v>
       </c>
     </row>
@@ -8656,34 +8652,34 @@
         <v>173000.39</v>
       </c>
       <c r="H57" s="44">
+        <f t="shared" si="13"/>
+        <v>173000.39</v>
+      </c>
+      <c r="I57" s="159">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J57" s="160">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="K57" s="160">
         <f t="shared" si="12"/>
-        <v>173000.39</v>
-      </c>
-      <c r="I57" s="159">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="J57" s="160">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="K57" s="160">
-        <f t="shared" si="11"/>
-        <v>190300</v>
-      </c>
-      <c r="L57" s="236">
+        <v>207600</v>
+      </c>
+      <c r="L57" s="195">
         <v>0</v>
       </c>
       <c r="M57" s="162">
+        <f t="shared" si="7"/>
+        <v>207600.39</v>
+      </c>
+      <c r="N57" s="162">
         <f t="shared" si="6"/>
-        <v>190300.39</v>
-      </c>
-      <c r="N57" s="162">
-        <f t="shared" si="5"/>
-        <v>201718.39</v>
+        <v>220056.39</v>
       </c>
       <c r="O57" s="141">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0.39000000000000018</v>
       </c>
     </row>
@@ -8710,30 +8706,30 @@
         <v>88924.4</v>
       </c>
       <c r="I58" s="159">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="J58" s="160">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="K58" s="160">
-        <f t="shared" si="11"/>
-        <v>103400</v>
-      </c>
-      <c r="L58" s="236">
+        <f t="shared" si="12"/>
+        <v>112800</v>
+      </c>
+      <c r="L58" s="195">
         <v>0</v>
       </c>
       <c r="M58" s="162">
+        <f t="shared" si="7"/>
+        <v>112800.4</v>
+      </c>
+      <c r="N58" s="162">
         <f t="shared" si="6"/>
-        <v>103400.4</v>
-      </c>
-      <c r="N58" s="162">
-        <f t="shared" si="5"/>
-        <v>109604.4</v>
+        <v>119568.4</v>
       </c>
       <c r="O58" s="141">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0.40000000000000019</v>
       </c>
     </row>
@@ -8760,30 +8756,30 @@
         <v>87000.41</v>
       </c>
       <c r="I59" s="159">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="J59" s="160">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="K59" s="160">
-        <f t="shared" si="11"/>
-        <v>95700</v>
-      </c>
-      <c r="L59" s="236">
+        <f t="shared" si="12"/>
+        <v>104400</v>
+      </c>
+      <c r="L59" s="195">
         <v>0</v>
       </c>
       <c r="M59" s="162">
+        <f t="shared" si="7"/>
+        <v>104400.41</v>
+      </c>
+      <c r="N59" s="162">
         <f t="shared" si="6"/>
-        <v>95700.41</v>
-      </c>
-      <c r="N59" s="162">
-        <f t="shared" si="5"/>
-        <v>101442.41</v>
+        <v>110664.41</v>
       </c>
       <c r="O59" s="141">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0.4100000000000002</v>
       </c>
       <c r="Q59" t="s">
@@ -8795,48 +8791,48 @@
         <v>125</v>
       </c>
       <c r="B60" s="6"/>
-      <c r="C60" s="254" t="s">
+      <c r="C60" s="207" t="s">
         <v>88</v>
       </c>
-      <c r="D60" s="255" t="s">
+      <c r="D60" s="208" t="s">
         <v>202</v>
       </c>
-      <c r="E60" s="256"/>
-      <c r="F60" s="257">
+      <c r="E60" s="209"/>
+      <c r="F60" s="210">
         <v>9.4999999999999998E-3</v>
       </c>
-      <c r="G60" s="258">
+      <c r="G60" s="211">
         <v>95000.42</v>
       </c>
-      <c r="H60" s="263">
-        <f t="shared" ref="H60:H67" si="13">G60</f>
+      <c r="H60" s="216">
+        <f t="shared" ref="H60:H67" si="14">G60</f>
         <v>95000.42</v>
       </c>
-      <c r="I60" s="259">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="J60" s="260">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="K60" s="260">
+      <c r="I60" s="212">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J60" s="213">
         <f t="shared" si="11"/>
-        <v>104500</v>
-      </c>
-      <c r="L60" s="261">
-        <v>0</v>
-      </c>
-      <c r="M60" s="262">
+        <v>0</v>
+      </c>
+      <c r="K60" s="213">
+        <f t="shared" si="12"/>
+        <v>114000</v>
+      </c>
+      <c r="L60" s="214">
+        <v>0</v>
+      </c>
+      <c r="M60" s="215">
+        <f t="shared" si="7"/>
+        <v>114000.42</v>
+      </c>
+      <c r="N60" s="215">
         <f t="shared" si="6"/>
-        <v>104500.42</v>
-      </c>
-      <c r="N60" s="262">
-        <f t="shared" si="5"/>
-        <v>110770.42</v>
+        <v>120840.42</v>
       </c>
       <c r="O60" s="141">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0.42000000000000021</v>
       </c>
       <c r="P60" t="s">
@@ -8862,34 +8858,34 @@
         <v>164000.43</v>
       </c>
       <c r="H61" s="44">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>164000.43</v>
       </c>
       <c r="I61" s="159">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="J61" s="160">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="K61" s="160">
-        <f t="shared" si="11"/>
-        <v>180400.00000000003</v>
-      </c>
-      <c r="L61" s="236">
+        <f t="shared" si="12"/>
+        <v>196800.00000000003</v>
+      </c>
+      <c r="L61" s="195">
         <v>0</v>
       </c>
       <c r="M61" s="162">
+        <f t="shared" si="7"/>
+        <v>196800.43</v>
+      </c>
+      <c r="N61" s="162">
         <f t="shared" si="6"/>
-        <v>180400.43</v>
-      </c>
-      <c r="N61" s="162">
-        <f t="shared" si="5"/>
-        <v>191224.43</v>
+        <v>208608.43</v>
       </c>
       <c r="O61" s="141">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0.43000000000000022</v>
       </c>
     </row>
@@ -8912,34 +8908,34 @@
         <v>72000.44</v>
       </c>
       <c r="H62" s="44">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>72000.44</v>
       </c>
       <c r="I62" s="159">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="J62" s="160">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="K62" s="160">
-        <f t="shared" si="11"/>
-        <v>79200</v>
-      </c>
-      <c r="L62" s="236">
+        <f t="shared" si="12"/>
+        <v>86400</v>
+      </c>
+      <c r="L62" s="195">
         <v>0</v>
       </c>
       <c r="M62" s="162">
+        <f t="shared" si="7"/>
+        <v>86400.44</v>
+      </c>
+      <c r="N62" s="162">
         <f t="shared" si="6"/>
-        <v>79200.44</v>
-      </c>
-      <c r="N62" s="162">
-        <f t="shared" si="5"/>
-        <v>83952.44</v>
+        <v>91584.44</v>
       </c>
       <c r="O62" s="141">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0.44000000000000022</v>
       </c>
     </row>
@@ -8962,34 +8958,34 @@
         <v>173000.45</v>
       </c>
       <c r="H63" s="44">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>173000.45</v>
       </c>
       <c r="I63" s="159">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="J63" s="160">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="K63" s="160">
-        <f t="shared" si="11"/>
-        <v>190300</v>
-      </c>
-      <c r="L63" s="236">
+        <f t="shared" si="12"/>
+        <v>207600</v>
+      </c>
+      <c r="L63" s="195">
         <v>36000</v>
       </c>
       <c r="M63" s="162">
+        <f t="shared" si="7"/>
+        <v>243600.45</v>
+      </c>
+      <c r="N63" s="162">
         <f t="shared" si="6"/>
-        <v>226300.45</v>
-      </c>
-      <c r="N63" s="162">
-        <f t="shared" si="5"/>
-        <v>239878.45</v>
+        <v>258216.45</v>
       </c>
       <c r="O63" s="141">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0.45000000000000023</v>
       </c>
     </row>
@@ -8998,50 +8994,50 @@
         <v>125</v>
       </c>
       <c r="B64" s="6"/>
-      <c r="C64" s="254" t="s">
+      <c r="C64" s="207" t="s">
         <v>92</v>
       </c>
-      <c r="D64" s="255" t="s">
+      <c r="D64" s="208" t="s">
         <v>205</v>
       </c>
-      <c r="E64" s="256" t="s">
+      <c r="E64" s="209" t="s">
         <v>279</v>
       </c>
-      <c r="F64" s="257">
+      <c r="F64" s="210">
         <v>9.4000000000000004E-3</v>
       </c>
-      <c r="G64" s="258">
+      <c r="G64" s="211">
         <v>94000.46</v>
       </c>
-      <c r="H64" s="263">
-        <f t="shared" si="13"/>
+      <c r="H64" s="216">
+        <f t="shared" si="14"/>
         <v>94000.46</v>
       </c>
-      <c r="I64" s="259">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="J64" s="260">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="K64" s="260">
+      <c r="I64" s="212">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J64" s="213">
         <f t="shared" si="11"/>
-        <v>103400</v>
-      </c>
-      <c r="L64" s="261">
-        <v>0</v>
-      </c>
-      <c r="M64" s="262">
+        <v>0</v>
+      </c>
+      <c r="K64" s="213">
+        <f t="shared" si="12"/>
+        <v>112800</v>
+      </c>
+      <c r="L64" s="214">
+        <v>0</v>
+      </c>
+      <c r="M64" s="215">
+        <f t="shared" si="7"/>
+        <v>112800.46</v>
+      </c>
+      <c r="N64" s="215">
         <f t="shared" si="6"/>
-        <v>103400.46</v>
-      </c>
-      <c r="N64" s="262">
-        <f t="shared" si="5"/>
-        <v>109604.46</v>
+        <v>119568.46</v>
       </c>
       <c r="O64" s="141">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0.46000000000000024</v>
       </c>
     </row>
@@ -9065,30 +9061,30 @@
       </c>
       <c r="H65" s="44"/>
       <c r="I65" s="159">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>-82199.53</v>
       </c>
       <c r="J65" s="160">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="K65" s="160">
-        <f t="shared" si="11"/>
-        <v>95700</v>
-      </c>
-      <c r="L65" s="236">
+        <f t="shared" si="12"/>
+        <v>104400</v>
+      </c>
+      <c r="L65" s="195">
         <v>0</v>
       </c>
       <c r="M65" s="162">
+        <f t="shared" si="7"/>
+        <v>22200.47</v>
+      </c>
+      <c r="N65" s="162">
         <f t="shared" si="6"/>
-        <v>13500.47</v>
-      </c>
-      <c r="N65" s="162">
-        <f t="shared" si="5"/>
-        <v>14310.47</v>
+        <v>23532.47</v>
       </c>
       <c r="O65" s="141">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0.47000000000000025</v>
       </c>
     </row>
@@ -9111,34 +9107,34 @@
         <v>95000.48</v>
       </c>
       <c r="H66" s="44">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>95000.48</v>
       </c>
       <c r="I66" s="159">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="J66" s="160">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="K66" s="160">
-        <f t="shared" si="11"/>
-        <v>104500</v>
-      </c>
-      <c r="L66" s="236">
+        <f t="shared" si="12"/>
+        <v>114000</v>
+      </c>
+      <c r="L66" s="195">
         <v>0</v>
       </c>
       <c r="M66" s="162">
+        <f t="shared" si="7"/>
+        <v>114000.48</v>
+      </c>
+      <c r="N66" s="162">
         <f t="shared" si="6"/>
-        <v>104500.48</v>
-      </c>
-      <c r="N66" s="162">
-        <f t="shared" si="5"/>
-        <v>110771.48</v>
+        <v>120841.48</v>
       </c>
       <c r="O66" s="141">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0.48000000000000026</v>
       </c>
     </row>
@@ -9161,34 +9157,34 @@
         <v>164000.49</v>
       </c>
       <c r="H67" s="44">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>164000.49</v>
       </c>
       <c r="I67" s="159">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="J67" s="160">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="K67" s="160">
-        <f t="shared" si="11"/>
-        <v>180400.00000000003</v>
-      </c>
-      <c r="L67" s="236">
+        <f t="shared" si="12"/>
+        <v>196800.00000000003</v>
+      </c>
+      <c r="L67" s="195">
         <v>0</v>
       </c>
       <c r="M67" s="162">
+        <f t="shared" si="7"/>
+        <v>196800.49</v>
+      </c>
+      <c r="N67" s="162">
         <f t="shared" si="6"/>
-        <v>180400.49</v>
-      </c>
-      <c r="N67" s="162">
-        <f t="shared" si="5"/>
-        <v>191225.49</v>
+        <v>208609.49</v>
       </c>
       <c r="O67" s="141">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0.49000000000000027</v>
       </c>
     </row>
@@ -9212,30 +9208,30 @@
       </c>
       <c r="H68" s="44"/>
       <c r="I68" s="159">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>253030.5</v>
       </c>
       <c r="J68" s="160">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="K68" s="160">
-        <f t="shared" si="11"/>
-        <v>79200</v>
-      </c>
-      <c r="L68" s="236">
+        <f t="shared" si="12"/>
+        <v>86400</v>
+      </c>
+      <c r="L68" s="195">
         <v>0</v>
       </c>
       <c r="M68" s="162">
+        <f t="shared" si="7"/>
+        <v>339431.5</v>
+      </c>
+      <c r="N68" s="162">
         <f t="shared" si="6"/>
-        <v>332231.5</v>
-      </c>
-      <c r="N68" s="162">
-        <f t="shared" si="5"/>
-        <v>352165.5</v>
+        <v>359797.5</v>
       </c>
       <c r="O68" s="141">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0.50000000000000022</v>
       </c>
     </row>
@@ -9258,34 +9254,34 @@
         <v>173000.51</v>
       </c>
       <c r="H69" s="44">
-        <f t="shared" ref="H69:H73" si="14">G69</f>
+        <f t="shared" ref="H69:H72" si="15">G69</f>
         <v>173000.51</v>
       </c>
       <c r="I69" s="159">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="J69" s="160">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="K69" s="160">
-        <f t="shared" si="11"/>
-        <v>190300</v>
-      </c>
-      <c r="L69" s="236">
+        <f t="shared" si="12"/>
+        <v>207600</v>
+      </c>
+      <c r="L69" s="195">
         <v>0</v>
       </c>
       <c r="M69" s="162">
+        <f t="shared" si="7"/>
+        <v>207600.51</v>
+      </c>
+      <c r="N69" s="162">
         <f t="shared" si="6"/>
-        <v>190300.51</v>
-      </c>
-      <c r="N69" s="162">
-        <f t="shared" si="5"/>
-        <v>201719.51</v>
+        <v>220057.51</v>
       </c>
       <c r="O69" s="141">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0.51000000000000023</v>
       </c>
     </row>
@@ -9294,47 +9290,47 @@
         <v>125</v>
       </c>
       <c r="B70" s="6"/>
-      <c r="C70" s="254" t="s">
+      <c r="C70" s="207" t="s">
         <v>98</v>
       </c>
-      <c r="D70" s="255" t="s">
+      <c r="D70" s="208" t="s">
         <v>210</v>
       </c>
-      <c r="E70" s="256"/>
-      <c r="F70" s="257">
+      <c r="E70" s="209"/>
+      <c r="F70" s="210">
         <v>9.4000000000000004E-3</v>
       </c>
-      <c r="G70" s="258">
+      <c r="G70" s="211">
         <v>88923.520000000004</v>
       </c>
-      <c r="H70" s="263">
+      <c r="H70" s="216">
         <v>89677.52</v>
       </c>
-      <c r="I70" s="259">
-        <f t="shared" si="0"/>
+      <c r="I70" s="212">
+        <f t="shared" si="1"/>
         <v>-754</v>
       </c>
-      <c r="J70" s="260">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="K70" s="260">
+      <c r="J70" s="213">
         <f t="shared" si="11"/>
-        <v>103400</v>
-      </c>
-      <c r="L70" s="261">
-        <v>0</v>
-      </c>
-      <c r="M70" s="262">
+        <v>0</v>
+      </c>
+      <c r="K70" s="213">
+        <f t="shared" si="12"/>
+        <v>112800</v>
+      </c>
+      <c r="L70" s="214">
+        <v>0</v>
+      </c>
+      <c r="M70" s="215">
+        <f t="shared" si="7"/>
+        <v>112046.52</v>
+      </c>
+      <c r="N70" s="215">
         <f t="shared" si="6"/>
-        <v>102646.52</v>
-      </c>
-      <c r="N70" s="262">
-        <f t="shared" si="5"/>
-        <v>108805.52</v>
+        <v>118769.52</v>
       </c>
       <c r="O70" s="141">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0.52000000000000024</v>
       </c>
     </row>
@@ -9357,34 +9353,34 @@
         <v>87000.53</v>
       </c>
       <c r="H71" s="44">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>87000.53</v>
       </c>
       <c r="I71" s="159">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="J71" s="160">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="K71" s="160">
-        <f t="shared" si="11"/>
-        <v>95700</v>
-      </c>
-      <c r="L71" s="236">
+        <f t="shared" si="12"/>
+        <v>104400</v>
+      </c>
+      <c r="L71" s="195">
         <v>0</v>
       </c>
       <c r="M71" s="162">
+        <f t="shared" si="7"/>
+        <v>104400.53</v>
+      </c>
+      <c r="N71" s="162">
         <f t="shared" si="6"/>
-        <v>95700.53</v>
-      </c>
-      <c r="N71" s="162">
-        <f t="shared" si="5"/>
-        <v>101443.53</v>
+        <v>110665.53</v>
       </c>
       <c r="O71" s="141">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0.53000000000000025</v>
       </c>
       <c r="Q71" t="s">
@@ -9410,34 +9406,34 @@
         <v>95000.54</v>
       </c>
       <c r="H72" s="44">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>95000.54</v>
       </c>
       <c r="I72" s="159">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="J72" s="160">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="K72" s="160">
-        <f t="shared" si="11"/>
-        <v>104500</v>
-      </c>
-      <c r="L72" s="236">
+        <f t="shared" si="12"/>
+        <v>114000</v>
+      </c>
+      <c r="L72" s="195">
         <v>0</v>
       </c>
       <c r="M72" s="162">
+        <f t="shared" si="7"/>
+        <v>114000.54</v>
+      </c>
+      <c r="N72" s="162">
         <f t="shared" si="6"/>
-        <v>104500.54</v>
-      </c>
-      <c r="N72" s="162">
-        <f t="shared" si="5"/>
-        <v>110771.54</v>
+        <v>120841.54</v>
       </c>
       <c r="O72" s="141">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0.54000000000000026</v>
       </c>
     </row>
@@ -9461,30 +9457,30 @@
       </c>
       <c r="H73" s="44"/>
       <c r="I73" s="159">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>235000.55</v>
       </c>
       <c r="J73" s="160">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="K73" s="160">
-        <f t="shared" si="11"/>
-        <v>258500</v>
-      </c>
-      <c r="L73" s="236">
+        <f t="shared" si="12"/>
+        <v>282000</v>
+      </c>
+      <c r="L73" s="195">
         <v>0</v>
       </c>
       <c r="M73" s="162">
+        <f t="shared" si="7"/>
+        <v>517001.55</v>
+      </c>
+      <c r="N73" s="162">
         <f t="shared" si="6"/>
-        <v>493501.55</v>
-      </c>
-      <c r="N73" s="162">
-        <f t="shared" si="5"/>
-        <v>523112.55</v>
+        <v>548022.55000000005</v>
       </c>
       <c r="O73" s="141">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0.55000000000000027</v>
       </c>
     </row>
@@ -9511,30 +9507,30 @@
         <v>163657.56</v>
       </c>
       <c r="I74" s="159">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="J74" s="160">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="K74" s="160">
-        <f t="shared" si="11"/>
-        <v>190300</v>
-      </c>
-      <c r="L74" s="236">
+        <f t="shared" si="12"/>
+        <v>207600</v>
+      </c>
+      <c r="L74" s="195">
         <v>0</v>
       </c>
       <c r="M74" s="162">
+        <f t="shared" si="7"/>
+        <v>207600.56</v>
+      </c>
+      <c r="N74" s="162">
         <f t="shared" si="6"/>
-        <v>190300.56</v>
-      </c>
-      <c r="N74" s="162">
-        <f t="shared" si="5"/>
-        <v>201719.56</v>
+        <v>220057.56</v>
       </c>
       <c r="O74" s="141">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0.56000000000000028</v>
       </c>
     </row>
@@ -9561,30 +9557,30 @@
         <v>94000.57</v>
       </c>
       <c r="I75" s="159">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="J75" s="160">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="K75" s="160">
-        <f t="shared" si="11"/>
-        <v>103400</v>
-      </c>
-      <c r="L75" s="236">
+        <f t="shared" si="12"/>
+        <v>112800</v>
+      </c>
+      <c r="L75" s="195">
         <v>0</v>
       </c>
       <c r="M75" s="162">
+        <f t="shared" si="7"/>
+        <v>112800.57</v>
+      </c>
+      <c r="N75" s="162">
         <f t="shared" si="6"/>
-        <v>103400.57</v>
-      </c>
-      <c r="N75" s="162">
-        <f t="shared" si="5"/>
-        <v>109605.57</v>
+        <v>119569.57</v>
       </c>
       <c r="O75" s="141">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0.57000000000000028</v>
       </c>
     </row>
@@ -9613,30 +9609,30 @@
         <v>92221.58</v>
       </c>
       <c r="I76" s="159">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="J76" s="160">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="K76" s="160">
-        <f t="shared" si="11"/>
-        <v>95700</v>
-      </c>
-      <c r="L76" s="236">
+        <f t="shared" si="12"/>
+        <v>104400</v>
+      </c>
+      <c r="L76" s="195">
         <v>12000</v>
       </c>
       <c r="M76" s="162">
+        <f t="shared" si="7"/>
+        <v>116400.58</v>
+      </c>
+      <c r="N76" s="162">
         <f t="shared" si="6"/>
-        <v>107700.58</v>
-      </c>
-      <c r="N76" s="162">
-        <f t="shared" si="5"/>
-        <v>114163.58</v>
+        <v>123385.58</v>
       </c>
       <c r="O76" s="141">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0.58000000000000029</v>
       </c>
     </row>
@@ -9662,30 +9658,30 @@
         <v>95262.59</v>
       </c>
       <c r="I77" s="159">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>-5393</v>
       </c>
       <c r="J77" s="160">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="K77" s="160">
-        <f t="shared" si="11"/>
-        <v>104500</v>
-      </c>
-      <c r="L77" s="236">
+        <f t="shared" si="12"/>
+        <v>114000</v>
+      </c>
+      <c r="L77" s="195">
         <v>0</v>
       </c>
       <c r="M77" s="162">
+        <f t="shared" si="7"/>
+        <v>108607.59</v>
+      </c>
+      <c r="N77" s="162">
         <f t="shared" si="6"/>
-        <v>99107.59</v>
-      </c>
-      <c r="N77" s="162">
-        <f t="shared" si="5"/>
-        <v>105054.59</v>
+        <v>115124.59</v>
       </c>
       <c r="O77" s="141">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0.5900000000000003</v>
       </c>
     </row>
@@ -9712,30 +9708,30 @@
         <v>452021.2</v>
       </c>
       <c r="I78" s="159">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>-5519.6000000000349</v>
       </c>
       <c r="J78" s="160">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="K78" s="160">
-        <f t="shared" si="11"/>
-        <v>258500</v>
-      </c>
-      <c r="L78" s="236">
+        <f t="shared" si="12"/>
+        <v>282000</v>
+      </c>
+      <c r="L78" s="195">
         <v>0</v>
       </c>
       <c r="M78" s="162">
+        <f t="shared" si="7"/>
+        <v>276480.59999999998</v>
+      </c>
+      <c r="N78" s="162">
         <f t="shared" si="6"/>
-        <v>252980.6</v>
-      </c>
-      <c r="N78" s="162">
-        <f t="shared" si="5"/>
-        <v>268159.59999999998</v>
+        <v>293069.59999999998</v>
       </c>
       <c r="O78" s="141">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0.60000000000000031</v>
       </c>
     </row>
@@ -9761,30 +9757,30 @@
         <v>173000.61</v>
       </c>
       <c r="I79" s="159">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="J79" s="160">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="K79" s="160">
-        <f t="shared" si="11"/>
-        <v>190300</v>
-      </c>
-      <c r="L79" s="236">
+        <f t="shared" si="12"/>
+        <v>207600</v>
+      </c>
+      <c r="L79" s="195">
         <v>0</v>
       </c>
       <c r="M79" s="162">
+        <f t="shared" si="7"/>
+        <v>207600.61</v>
+      </c>
+      <c r="N79" s="162">
         <f t="shared" si="6"/>
-        <v>190300.61</v>
-      </c>
-      <c r="N79" s="162">
-        <f t="shared" si="5"/>
-        <v>201719.61</v>
+        <v>220057.61</v>
       </c>
       <c r="O79" s="141">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0.61000000000000032</v>
       </c>
     </row>
@@ -9808,30 +9804,30 @@
       </c>
       <c r="H80" s="44"/>
       <c r="I80" s="159">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>122200.62</v>
       </c>
       <c r="J80" s="160">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="K80" s="160">
-        <f t="shared" si="11"/>
-        <v>103400</v>
-      </c>
-      <c r="L80" s="236">
+        <f t="shared" si="12"/>
+        <v>112800</v>
+      </c>
+      <c r="L80" s="195">
         <v>12000</v>
       </c>
       <c r="M80" s="162">
+        <f t="shared" si="7"/>
+        <v>247001.62</v>
+      </c>
+      <c r="N80" s="162">
         <f t="shared" si="6"/>
-        <v>237601.62</v>
-      </c>
-      <c r="N80" s="162">
-        <f t="shared" si="5"/>
-        <v>251858.62</v>
+        <v>261822.62</v>
       </c>
       <c r="O80" s="141">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0.62000000000000033</v>
       </c>
     </row>
@@ -9860,30 +9856,30 @@
         <v>87000.63</v>
       </c>
       <c r="I81" s="159">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="J81" s="160">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="K81" s="160">
-        <f t="shared" si="11"/>
-        <v>95700</v>
-      </c>
-      <c r="L81" s="236">
+        <f t="shared" si="12"/>
+        <v>104400</v>
+      </c>
+      <c r="L81" s="195">
         <v>0</v>
       </c>
       <c r="M81" s="162">
+        <f t="shared" si="7"/>
+        <v>104400.63</v>
+      </c>
+      <c r="N81" s="162">
         <f t="shared" si="6"/>
-        <v>95700.63</v>
-      </c>
-      <c r="N81" s="162">
-        <f t="shared" si="5"/>
-        <v>101443.63</v>
+        <v>110665.63</v>
       </c>
       <c r="O81" s="141">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0.63000000000000034</v>
       </c>
     </row>
@@ -9910,30 +9906,30 @@
         <v>95000.639999999999</v>
       </c>
       <c r="I82" s="159">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="J82" s="160">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="K82" s="160">
-        <f t="shared" si="11"/>
-        <v>104500</v>
-      </c>
-      <c r="L82" s="236">
+        <f t="shared" si="12"/>
+        <v>114000</v>
+      </c>
+      <c r="L82" s="195">
         <v>0</v>
       </c>
       <c r="M82" s="162">
+        <f t="shared" si="7"/>
+        <v>114000.64</v>
+      </c>
+      <c r="N82" s="162">
         <f t="shared" si="6"/>
-        <v>104500.64</v>
-      </c>
-      <c r="N82" s="162">
-        <f t="shared" si="5"/>
-        <v>110771.64</v>
+        <v>120841.64</v>
       </c>
       <c r="O82" s="141">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0.64000000000000035</v>
       </c>
       <c r="P82" t="s">
@@ -9963,30 +9959,30 @@
         <v>234999.65</v>
       </c>
       <c r="I83" s="159">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="J83" s="160">
-        <f t="shared" ref="J83:J114" si="15">M$8*F83</f>
+        <f t="shared" ref="J83:J114" si="16">M$8*F83</f>
         <v>0</v>
       </c>
       <c r="K83" s="160">
-        <f t="shared" ref="K83:K114" si="16">M$2*F83</f>
-        <v>258500</v>
-      </c>
-      <c r="L83" s="236">
+        <f t="shared" ref="K83:K114" si="17">M$2*F83</f>
+        <v>282000</v>
+      </c>
+      <c r="L83" s="195">
         <v>0</v>
       </c>
       <c r="M83" s="162">
+        <f t="shared" si="7"/>
+        <v>282000.65000000002</v>
+      </c>
+      <c r="N83" s="162">
         <f t="shared" si="6"/>
-        <v>258500.65</v>
-      </c>
-      <c r="N83" s="162">
-        <f t="shared" si="5"/>
-        <v>274011.65000000002</v>
+        <v>298921.65000000002</v>
       </c>
       <c r="O83" s="141">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0.65000000000000036</v>
       </c>
     </row>
@@ -10009,34 +10005,34 @@
         <v>173000.66</v>
       </c>
       <c r="H84" s="44">
-        <f t="shared" ref="H84:H92" si="17">G84</f>
+        <f t="shared" ref="H84:H92" si="18">G84</f>
         <v>173000.66</v>
       </c>
       <c r="I84" s="159">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="J84" s="160">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="K84" s="160">
-        <f t="shared" si="16"/>
-        <v>190300</v>
-      </c>
-      <c r="L84" s="236">
+        <f t="shared" si="17"/>
+        <v>207600</v>
+      </c>
+      <c r="L84" s="195">
         <v>0</v>
       </c>
       <c r="M84" s="162">
-        <f t="shared" ref="M84:M131" si="18">ROUND((K84+J84+I84+L84),0) + O84</f>
-        <v>190300.66</v>
+        <f t="shared" ref="M84:M131" si="19">ROUND((K84+J84+I84+L84),0) + O84</f>
+        <v>207600.66</v>
       </c>
       <c r="N84" s="162">
-        <f t="shared" ref="N84:N131" si="19">ROUND((M84*6% + M84 ),0) + O84</f>
-        <v>201719.66</v>
+        <f t="shared" ref="N84:N131" si="20">ROUND((M84*6% + M84 ),0) + O84</f>
+        <v>220057.66</v>
       </c>
       <c r="O84" s="141">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0.66000000000000036</v>
       </c>
     </row>
@@ -10059,34 +10055,34 @@
         <v>94000.67</v>
       </c>
       <c r="H85" s="44">
+        <f t="shared" si="18"/>
+        <v>94000.67</v>
+      </c>
+      <c r="I85" s="159">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J85" s="160">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="K85" s="160">
         <f t="shared" si="17"/>
-        <v>94000.67</v>
-      </c>
-      <c r="I85" s="159">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="J85" s="160">
-        <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="K85" s="160">
-        <f t="shared" si="16"/>
-        <v>103400</v>
-      </c>
-      <c r="L85" s="236">
+        <v>112800</v>
+      </c>
+      <c r="L85" s="195">
         <v>0</v>
       </c>
       <c r="M85" s="162">
-        <f t="shared" si="18"/>
-        <v>103400.67</v>
+        <f t="shared" si="19"/>
+        <v>112800.67</v>
       </c>
       <c r="N85" s="162">
-        <f t="shared" si="19"/>
-        <v>109605.67</v>
+        <f t="shared" si="20"/>
+        <v>119569.67</v>
       </c>
       <c r="O85" s="141">
-        <f t="shared" ref="O85:O131" si="20">O84+0.01</f>
+        <f t="shared" ref="O85:O131" si="21">O84+0.01</f>
         <v>0.67000000000000037</v>
       </c>
     </row>
@@ -10113,30 +10109,30 @@
         <v>87000.68</v>
       </c>
       <c r="I86" s="159">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="J86" s="160">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="K86" s="160">
-        <f t="shared" si="16"/>
-        <v>95700</v>
-      </c>
-      <c r="L86" s="236">
+        <f t="shared" si="17"/>
+        <v>104400</v>
+      </c>
+      <c r="L86" s="195">
         <v>0</v>
       </c>
       <c r="M86" s="162">
-        <f t="shared" si="18"/>
-        <v>95700.68</v>
+        <f t="shared" si="19"/>
+        <v>104400.68</v>
       </c>
       <c r="N86" s="162">
-        <f t="shared" si="19"/>
-        <v>101443.68</v>
+        <f t="shared" si="20"/>
+        <v>110665.68</v>
       </c>
       <c r="O86" s="141">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>0.68000000000000038</v>
       </c>
     </row>
@@ -10163,28 +10159,28 @@
         <v>123500.69</v>
       </c>
       <c r="I87" s="159">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="J87" s="160">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="K87" s="160">
-        <f t="shared" si="16"/>
-        <v>104500</v>
-      </c>
-      <c r="L87" s="236"/>
+        <f t="shared" si="17"/>
+        <v>114000</v>
+      </c>
+      <c r="L87" s="195"/>
       <c r="M87" s="162">
-        <f t="shared" si="18"/>
-        <v>104500.69</v>
+        <f t="shared" si="19"/>
+        <v>114000.69</v>
       </c>
       <c r="N87" s="162">
-        <f t="shared" si="19"/>
-        <v>110771.69</v>
+        <f t="shared" si="20"/>
+        <v>120841.69</v>
       </c>
       <c r="O87" s="141">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>0.69000000000000039</v>
       </c>
     </row>
@@ -10205,34 +10201,34 @@
         <v>23000.7</v>
       </c>
       <c r="H88" s="44">
+        <f t="shared" si="18"/>
+        <v>23000.7</v>
+      </c>
+      <c r="I88" s="159">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J88" s="160">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="K88" s="160">
         <f t="shared" si="17"/>
-        <v>23000.7</v>
-      </c>
-      <c r="I88" s="159">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="J88" s="160">
-        <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="K88" s="160">
-        <f t="shared" si="16"/>
-        <v>25300</v>
-      </c>
-      <c r="L88" s="236">
+        <v>27600</v>
+      </c>
+      <c r="L88" s="195">
         <v>0</v>
       </c>
       <c r="M88" s="162">
-        <f t="shared" si="18"/>
-        <v>25300.7</v>
+        <f t="shared" si="19"/>
+        <v>27600.7</v>
       </c>
       <c r="N88" s="162">
-        <f t="shared" si="19"/>
-        <v>26819.7</v>
+        <f t="shared" si="20"/>
+        <v>29257.7</v>
       </c>
       <c r="O88" s="141">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>0.7000000000000004</v>
       </c>
     </row>
@@ -10253,34 +10249,34 @@
         <v>23000.71</v>
       </c>
       <c r="H89" s="44">
+        <f t="shared" si="18"/>
+        <v>23000.71</v>
+      </c>
+      <c r="I89" s="159">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J89" s="160">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="K89" s="160">
         <f t="shared" si="17"/>
-        <v>23000.71</v>
-      </c>
-      <c r="I89" s="159">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="J89" s="160">
-        <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="K89" s="160">
-        <f t="shared" si="16"/>
-        <v>25300</v>
-      </c>
-      <c r="L89" s="236">
+        <v>27600</v>
+      </c>
+      <c r="L89" s="195">
         <v>0</v>
       </c>
       <c r="M89" s="162">
-        <f t="shared" si="18"/>
-        <v>25300.71</v>
+        <f t="shared" si="19"/>
+        <v>27600.71</v>
       </c>
       <c r="N89" s="162">
-        <f t="shared" si="19"/>
-        <v>26819.71</v>
+        <f t="shared" si="20"/>
+        <v>29257.71</v>
       </c>
       <c r="O89" s="141">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>0.71000000000000041</v>
       </c>
     </row>
@@ -10305,30 +10301,30 @@
         <v>21757.72</v>
       </c>
       <c r="I90" s="159">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="J90" s="160">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="K90" s="160">
-        <f t="shared" si="16"/>
-        <v>25300</v>
-      </c>
-      <c r="L90" s="236">
+        <f t="shared" si="17"/>
+        <v>27600</v>
+      </c>
+      <c r="L90" s="195">
         <v>0</v>
       </c>
       <c r="M90" s="162">
-        <f t="shared" si="18"/>
-        <v>25300.720000000001</v>
+        <f t="shared" si="19"/>
+        <v>27600.720000000001</v>
       </c>
       <c r="N90" s="162">
-        <f t="shared" si="19"/>
-        <v>26819.72</v>
+        <f t="shared" si="20"/>
+        <v>29257.72</v>
       </c>
       <c r="O90" s="141">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>0.72000000000000042</v>
       </c>
     </row>
@@ -10349,82 +10345,82 @@
         <v>23000.73</v>
       </c>
       <c r="H91" s="44">
+        <f t="shared" si="18"/>
+        <v>23000.73</v>
+      </c>
+      <c r="I91" s="159">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J91" s="160">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="K91" s="160">
         <f t="shared" si="17"/>
-        <v>23000.73</v>
-      </c>
-      <c r="I91" s="159">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="J91" s="160">
-        <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="K91" s="160">
-        <f t="shared" si="16"/>
-        <v>25300</v>
-      </c>
-      <c r="L91" s="236">
+        <v>27600</v>
+      </c>
+      <c r="L91" s="195">
         <v>0</v>
       </c>
       <c r="M91" s="162">
-        <f t="shared" si="18"/>
-        <v>25300.73</v>
+        <f t="shared" si="19"/>
+        <v>27600.73</v>
       </c>
       <c r="N91" s="162">
-        <f t="shared" si="19"/>
-        <v>26819.73</v>
+        <f t="shared" si="20"/>
+        <v>29257.73</v>
       </c>
       <c r="O91" s="141">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>0.73000000000000043</v>
       </c>
     </row>
     <row r="92" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A92" s="114"/>
       <c r="B92" s="35"/>
-      <c r="C92" s="273" t="s">
+      <c r="C92" s="223" t="s">
         <v>131</v>
       </c>
-      <c r="D92" s="274" t="s">
+      <c r="D92" s="224" t="s">
         <v>202</v>
       </c>
-      <c r="E92" s="274"/>
-      <c r="F92" s="275">
+      <c r="E92" s="224"/>
+      <c r="F92" s="225">
         <v>2.3E-3</v>
       </c>
-      <c r="G92" s="263">
+      <c r="G92" s="216">
         <v>23000.74</v>
       </c>
-      <c r="H92" s="263">
+      <c r="H92" s="216">
+        <f t="shared" si="18"/>
+        <v>23000.74</v>
+      </c>
+      <c r="I92" s="226">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J92" s="227">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="K92" s="227">
         <f t="shared" si="17"/>
-        <v>23000.74</v>
-      </c>
-      <c r="I92" s="276">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="J92" s="277">
-        <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="K92" s="277">
-        <f t="shared" si="16"/>
-        <v>25300</v>
-      </c>
-      <c r="L92" s="278">
-        <v>0</v>
-      </c>
-      <c r="M92" s="279">
-        <f t="shared" si="18"/>
-        <v>25300.74</v>
-      </c>
-      <c r="N92" s="279">
+        <v>27600</v>
+      </c>
+      <c r="L92" s="228">
+        <v>0</v>
+      </c>
+      <c r="M92" s="229">
         <f t="shared" si="19"/>
-        <v>26819.74</v>
+        <v>27600.74</v>
+      </c>
+      <c r="N92" s="229">
+        <f t="shared" si="20"/>
+        <v>29257.74</v>
       </c>
       <c r="O92" s="141">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>0.74000000000000044</v>
       </c>
       <c r="P92" t="s">
@@ -10452,30 +10448,30 @@
         <v>85682.75</v>
       </c>
       <c r="I93" s="159">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="J93" s="160">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="K93" s="160">
-        <f t="shared" si="16"/>
-        <v>25300</v>
-      </c>
-      <c r="L93" s="236">
+        <f t="shared" si="17"/>
+        <v>27600</v>
+      </c>
+      <c r="L93" s="195">
         <v>0</v>
       </c>
       <c r="M93" s="162">
-        <f t="shared" si="18"/>
-        <v>25300.75</v>
+        <f t="shared" si="19"/>
+        <v>27600.75</v>
       </c>
       <c r="N93" s="162">
-        <f t="shared" si="19"/>
-        <v>26819.75</v>
+        <f t="shared" si="20"/>
+        <v>29257.75</v>
       </c>
       <c r="O93" s="141">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>0.75000000000000044</v>
       </c>
     </row>
@@ -10500,30 +10496,30 @@
         <v>23000.76</v>
       </c>
       <c r="I94" s="159">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="J94" s="160">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="K94" s="160">
-        <f t="shared" si="16"/>
-        <v>25300</v>
-      </c>
-      <c r="L94" s="236">
+        <f t="shared" si="17"/>
+        <v>27600</v>
+      </c>
+      <c r="L94" s="195">
         <v>0</v>
       </c>
       <c r="M94" s="162">
-        <f t="shared" si="18"/>
-        <v>25300.76</v>
+        <f t="shared" si="19"/>
+        <v>27600.76</v>
       </c>
       <c r="N94" s="162">
-        <f t="shared" si="19"/>
-        <v>26819.759999999998</v>
+        <f t="shared" si="20"/>
+        <v>29257.759999999998</v>
       </c>
       <c r="O94" s="141">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>0.76000000000000045</v>
       </c>
     </row>
@@ -10548,30 +10544,30 @@
         <v>23000.77</v>
       </c>
       <c r="I95" s="159">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="J95" s="160">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="K95" s="160">
-        <f t="shared" si="16"/>
-        <v>25300</v>
-      </c>
-      <c r="L95" s="236">
+        <f t="shared" si="17"/>
+        <v>27600</v>
+      </c>
+      <c r="L95" s="195">
         <v>0</v>
       </c>
       <c r="M95" s="162">
-        <f t="shared" si="18"/>
-        <v>25300.77</v>
+        <f t="shared" si="19"/>
+        <v>27600.77</v>
       </c>
       <c r="N95" s="162">
-        <f t="shared" si="19"/>
-        <v>26819.77</v>
+        <f t="shared" si="20"/>
+        <v>29257.77</v>
       </c>
       <c r="O95" s="141">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>0.77000000000000046</v>
       </c>
     </row>
@@ -10595,30 +10591,30 @@
         <v>24381.78</v>
       </c>
       <c r="I96" s="159">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>-1381</v>
       </c>
       <c r="J96" s="160">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="K96" s="160">
-        <f t="shared" si="16"/>
-        <v>25300</v>
-      </c>
-      <c r="L96" s="236">
+        <f t="shared" si="17"/>
+        <v>27600</v>
+      </c>
+      <c r="L96" s="195">
         <v>0</v>
       </c>
       <c r="M96" s="162">
-        <f t="shared" si="18"/>
-        <v>23919.78</v>
+        <f t="shared" si="19"/>
+        <v>26219.78</v>
       </c>
       <c r="N96" s="162">
-        <f t="shared" si="19"/>
-        <v>25355.78</v>
+        <f t="shared" si="20"/>
+        <v>27793.78</v>
       </c>
       <c r="O96" s="141">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>0.78000000000000047</v>
       </c>
     </row>
@@ -10640,30 +10636,30 @@
       </c>
       <c r="H97" s="44"/>
       <c r="I97" s="159">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>80831.789999999994</v>
       </c>
       <c r="J97" s="160">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="K97" s="160">
-        <f t="shared" si="16"/>
-        <v>25300</v>
-      </c>
-      <c r="L97" s="236">
+        <f t="shared" si="17"/>
+        <v>27600</v>
+      </c>
+      <c r="L97" s="195">
         <v>0</v>
       </c>
       <c r="M97" s="162">
-        <f t="shared" si="18"/>
-        <v>106132.79</v>
+        <f t="shared" si="19"/>
+        <v>108432.79</v>
       </c>
       <c r="N97" s="162">
-        <f t="shared" si="19"/>
-        <v>112501.79</v>
+        <f t="shared" si="20"/>
+        <v>114939.79</v>
       </c>
       <c r="O97" s="141">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>0.79000000000000048</v>
       </c>
     </row>
@@ -10684,34 +10680,34 @@
         <v>23000.799999999999</v>
       </c>
       <c r="H98" s="44">
-        <f t="shared" ref="H98:H104" si="21">G98</f>
+        <f t="shared" ref="H98:H104" si="22">G98</f>
         <v>23000.799999999999</v>
       </c>
       <c r="I98" s="159">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="J98" s="160">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="K98" s="160">
-        <f t="shared" si="16"/>
-        <v>25300</v>
-      </c>
-      <c r="L98" s="236">
+        <f t="shared" si="17"/>
+        <v>27600</v>
+      </c>
+      <c r="L98" s="195">
         <v>0</v>
       </c>
       <c r="M98" s="162">
-        <f t="shared" si="18"/>
-        <v>25300.799999999999</v>
+        <f t="shared" si="19"/>
+        <v>27600.799999999999</v>
       </c>
       <c r="N98" s="162">
-        <f t="shared" si="19"/>
-        <v>26819.8</v>
+        <f t="shared" si="20"/>
+        <v>29257.8</v>
       </c>
       <c r="O98" s="141">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>0.80000000000000049</v>
       </c>
     </row>
@@ -10732,34 +10728,34 @@
         <v>23000.81</v>
       </c>
       <c r="H99" s="90">
+        <f t="shared" si="22"/>
+        <v>23000.81</v>
+      </c>
+      <c r="I99" s="56">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J99" s="26">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="K99" s="26">
+        <f t="shared" si="17"/>
+        <v>27600</v>
+      </c>
+      <c r="L99" s="195">
+        <v>0</v>
+      </c>
+      <c r="M99" s="8">
+        <f t="shared" si="19"/>
+        <v>27600.81</v>
+      </c>
+      <c r="N99" s="8">
+        <f t="shared" si="20"/>
+        <v>29257.81</v>
+      </c>
+      <c r="O99" s="141">
         <f t="shared" si="21"/>
-        <v>23000.81</v>
-      </c>
-      <c r="I99" s="56">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="J99" s="26">
-        <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="K99" s="26">
-        <f t="shared" si="16"/>
-        <v>25300</v>
-      </c>
-      <c r="L99" s="236">
-        <v>0</v>
-      </c>
-      <c r="M99" s="8">
-        <f t="shared" si="18"/>
-        <v>25300.81</v>
-      </c>
-      <c r="N99" s="8">
-        <f t="shared" si="19"/>
-        <v>26819.81</v>
-      </c>
-      <c r="O99" s="141">
-        <f t="shared" si="20"/>
         <v>0.8100000000000005</v>
       </c>
     </row>
@@ -10780,34 +10776,34 @@
         <v>23000.82</v>
       </c>
       <c r="H100" s="90">
+        <f t="shared" si="22"/>
+        <v>23000.82</v>
+      </c>
+      <c r="I100" s="56">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J100" s="26">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="K100" s="26">
+        <f t="shared" si="17"/>
+        <v>27600</v>
+      </c>
+      <c r="L100" s="195">
+        <v>0</v>
+      </c>
+      <c r="M100" s="8">
+        <f t="shared" si="19"/>
+        <v>27600.82</v>
+      </c>
+      <c r="N100" s="8">
+        <f t="shared" si="20"/>
+        <v>29257.82</v>
+      </c>
+      <c r="O100" s="141">
         <f t="shared" si="21"/>
-        <v>23000.82</v>
-      </c>
-      <c r="I100" s="56">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="J100" s="26">
-        <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="K100" s="26">
-        <f t="shared" si="16"/>
-        <v>25300</v>
-      </c>
-      <c r="L100" s="236">
-        <v>0</v>
-      </c>
-      <c r="M100" s="8">
-        <f t="shared" si="18"/>
-        <v>25300.82</v>
-      </c>
-      <c r="N100" s="8">
-        <f t="shared" si="19"/>
-        <v>26819.82</v>
-      </c>
-      <c r="O100" s="141">
-        <f t="shared" si="20"/>
         <v>0.82000000000000051</v>
       </c>
     </row>
@@ -10828,34 +10824,34 @@
         <v>23000.83</v>
       </c>
       <c r="H101" s="90">
+        <f t="shared" si="22"/>
+        <v>23000.83</v>
+      </c>
+      <c r="I101" s="56">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J101" s="26">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="K101" s="26">
+        <f t="shared" si="17"/>
+        <v>27600</v>
+      </c>
+      <c r="L101" s="195">
+        <v>0</v>
+      </c>
+      <c r="M101" s="8">
+        <f t="shared" si="19"/>
+        <v>27600.83</v>
+      </c>
+      <c r="N101" s="8">
+        <f t="shared" si="20"/>
+        <v>29257.83</v>
+      </c>
+      <c r="O101" s="141">
         <f t="shared" si="21"/>
-        <v>23000.83</v>
-      </c>
-      <c r="I101" s="56">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="J101" s="26">
-        <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="K101" s="26">
-        <f t="shared" si="16"/>
-        <v>25300</v>
-      </c>
-      <c r="L101" s="236">
-        <v>0</v>
-      </c>
-      <c r="M101" s="8">
-        <f t="shared" si="18"/>
-        <v>25300.83</v>
-      </c>
-      <c r="N101" s="8">
-        <f t="shared" si="19"/>
-        <v>26819.83</v>
-      </c>
-      <c r="O101" s="141">
-        <f t="shared" si="20"/>
         <v>0.83000000000000052</v>
       </c>
     </row>
@@ -10876,82 +10872,82 @@
         <v>23000.84</v>
       </c>
       <c r="H102" s="90">
+        <f t="shared" si="22"/>
+        <v>23000.84</v>
+      </c>
+      <c r="I102" s="56">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J102" s="26">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="K102" s="26">
+        <f t="shared" si="17"/>
+        <v>27600</v>
+      </c>
+      <c r="L102" s="195">
+        <v>0</v>
+      </c>
+      <c r="M102" s="8">
+        <f t="shared" si="19"/>
+        <v>27600.84</v>
+      </c>
+      <c r="N102" s="8">
+        <f t="shared" si="20"/>
+        <v>29257.84</v>
+      </c>
+      <c r="O102" s="141">
         <f t="shared" si="21"/>
-        <v>23000.84</v>
-      </c>
-      <c r="I102" s="56">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="J102" s="26">
-        <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="K102" s="26">
-        <f t="shared" si="16"/>
-        <v>25300</v>
-      </c>
-      <c r="L102" s="236">
-        <v>0</v>
-      </c>
-      <c r="M102" s="8">
-        <f t="shared" si="18"/>
-        <v>25300.84</v>
-      </c>
-      <c r="N102" s="8">
-        <f t="shared" si="19"/>
-        <v>26819.84</v>
-      </c>
-      <c r="O102" s="141">
-        <f t="shared" si="20"/>
         <v>0.84000000000000052</v>
       </c>
     </row>
     <row r="103" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A103" s="114"/>
       <c r="B103" s="35"/>
-      <c r="C103" s="254" t="s">
+      <c r="C103" s="207" t="s">
         <v>142</v>
       </c>
-      <c r="D103" s="255" t="s">
+      <c r="D103" s="208" t="s">
         <v>225</v>
       </c>
-      <c r="E103" s="255"/>
-      <c r="F103" s="264">
+      <c r="E103" s="208"/>
+      <c r="F103" s="217">
         <v>2.3E-3</v>
       </c>
-      <c r="G103" s="258">
+      <c r="G103" s="211">
         <v>23000.85</v>
       </c>
-      <c r="H103" s="263">
+      <c r="H103" s="216">
+        <f t="shared" si="22"/>
+        <v>23000.85</v>
+      </c>
+      <c r="I103" s="212">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J103" s="213">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="K103" s="213">
+        <f t="shared" si="17"/>
+        <v>27600</v>
+      </c>
+      <c r="L103" s="214">
+        <v>0</v>
+      </c>
+      <c r="M103" s="215">
+        <f t="shared" si="19"/>
+        <v>27600.85</v>
+      </c>
+      <c r="N103" s="215">
+        <f t="shared" si="20"/>
+        <v>29257.85</v>
+      </c>
+      <c r="O103" s="141">
         <f t="shared" si="21"/>
-        <v>23000.85</v>
-      </c>
-      <c r="I103" s="259">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="J103" s="260">
-        <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="K103" s="260">
-        <f t="shared" si="16"/>
-        <v>25300</v>
-      </c>
-      <c r="L103" s="261">
-        <v>0</v>
-      </c>
-      <c r="M103" s="262">
-        <f t="shared" si="18"/>
-        <v>25300.85</v>
-      </c>
-      <c r="N103" s="262">
-        <f t="shared" si="19"/>
-        <v>26819.85</v>
-      </c>
-      <c r="O103" s="141">
-        <f t="shared" si="20"/>
         <v>0.85000000000000053</v>
       </c>
     </row>
@@ -10972,34 +10968,34 @@
         <v>23000.86</v>
       </c>
       <c r="H104" s="90">
+        <f t="shared" si="22"/>
+        <v>23000.86</v>
+      </c>
+      <c r="I104" s="56">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J104" s="26">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="K104" s="26">
+        <f t="shared" si="17"/>
+        <v>27600</v>
+      </c>
+      <c r="L104" s="195">
+        <v>0</v>
+      </c>
+      <c r="M104" s="8">
+        <f t="shared" si="19"/>
+        <v>27600.86</v>
+      </c>
+      <c r="N104" s="8">
+        <f t="shared" si="20"/>
+        <v>29257.86</v>
+      </c>
+      <c r="O104" s="141">
         <f t="shared" si="21"/>
-        <v>23000.86</v>
-      </c>
-      <c r="I104" s="56">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="J104" s="26">
-        <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="K104" s="26">
-        <f t="shared" si="16"/>
-        <v>25300</v>
-      </c>
-      <c r="L104" s="236">
-        <v>0</v>
-      </c>
-      <c r="M104" s="8">
-        <f t="shared" si="18"/>
-        <v>25300.86</v>
-      </c>
-      <c r="N104" s="8">
-        <f t="shared" si="19"/>
-        <v>26819.86</v>
-      </c>
-      <c r="O104" s="141">
-        <f t="shared" si="20"/>
         <v>0.86000000000000054</v>
       </c>
     </row>
@@ -11020,34 +11016,34 @@
         <v>23000.87</v>
       </c>
       <c r="H105" s="90">
-        <f t="shared" ref="H105:H111" si="22">G105</f>
+        <f t="shared" ref="H105:H111" si="23">G105</f>
         <v>23000.87</v>
       </c>
       <c r="I105" s="56">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="J105" s="26">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="K105" s="26">
-        <f t="shared" si="16"/>
-        <v>25300</v>
-      </c>
-      <c r="L105" s="236">
+        <f t="shared" si="17"/>
+        <v>27600</v>
+      </c>
+      <c r="L105" s="195">
         <v>0</v>
       </c>
       <c r="M105" s="8">
-        <f t="shared" si="18"/>
-        <v>25300.87</v>
+        <f t="shared" si="19"/>
+        <v>27600.87</v>
       </c>
       <c r="N105" s="8">
-        <f t="shared" si="19"/>
-        <v>26819.87</v>
+        <f t="shared" si="20"/>
+        <v>29257.87</v>
       </c>
       <c r="O105" s="141">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>0.87000000000000055</v>
       </c>
     </row>
@@ -11071,30 +11067,30 @@
         <v>23063.88</v>
       </c>
       <c r="I106" s="56">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>-1306</v>
       </c>
       <c r="J106" s="26">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="K106" s="26">
-        <f t="shared" si="16"/>
-        <v>25300</v>
-      </c>
-      <c r="L106" s="236">
+        <f t="shared" si="17"/>
+        <v>27600</v>
+      </c>
+      <c r="L106" s="195">
         <v>0</v>
       </c>
       <c r="M106" s="8">
-        <f t="shared" si="18"/>
-        <v>23994.880000000001</v>
+        <f t="shared" si="19"/>
+        <v>26294.880000000001</v>
       </c>
       <c r="N106" s="8">
-        <f t="shared" si="19"/>
-        <v>25435.88</v>
+        <f t="shared" si="20"/>
+        <v>27873.88</v>
       </c>
       <c r="O106" s="141">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>0.88000000000000056</v>
       </c>
     </row>
@@ -11115,34 +11111,34 @@
         <v>23000.89</v>
       </c>
       <c r="H107" s="90">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>23000.89</v>
       </c>
       <c r="I107" s="56">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="J107" s="26">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="K107" s="26">
-        <f t="shared" si="16"/>
-        <v>25300</v>
-      </c>
-      <c r="L107" s="236">
+        <f t="shared" si="17"/>
+        <v>27600</v>
+      </c>
+      <c r="L107" s="195">
         <v>0</v>
       </c>
       <c r="M107" s="8">
-        <f t="shared" si="18"/>
-        <v>25300.89</v>
+        <f t="shared" si="19"/>
+        <v>27600.89</v>
       </c>
       <c r="N107" s="8">
-        <f t="shared" si="19"/>
-        <v>26819.89</v>
+        <f t="shared" si="20"/>
+        <v>29257.89</v>
       </c>
       <c r="O107" s="141">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>0.89000000000000057</v>
       </c>
     </row>
@@ -11163,34 +11159,34 @@
         <v>23000.9</v>
       </c>
       <c r="H108" s="90">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>23000.9</v>
       </c>
       <c r="I108" s="56">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="J108" s="26">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="K108" s="26">
-        <f t="shared" si="16"/>
-        <v>25300</v>
-      </c>
-      <c r="L108" s="236">
+        <f t="shared" si="17"/>
+        <v>27600</v>
+      </c>
+      <c r="L108" s="195">
         <v>0</v>
       </c>
       <c r="M108" s="8">
-        <f t="shared" si="18"/>
-        <v>25300.9</v>
+        <f t="shared" si="19"/>
+        <v>27600.9</v>
       </c>
       <c r="N108" s="8">
-        <f t="shared" si="19"/>
-        <v>26819.9</v>
+        <f t="shared" si="20"/>
+        <v>29257.9</v>
       </c>
       <c r="O108" s="141">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>0.90000000000000058</v>
       </c>
     </row>
@@ -11211,34 +11207,34 @@
         <v>23000.91</v>
       </c>
       <c r="H109" s="90">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>23000.91</v>
       </c>
       <c r="I109" s="56">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="J109" s="26">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="K109" s="26">
-        <f t="shared" si="16"/>
-        <v>25300</v>
-      </c>
-      <c r="L109" s="236">
+        <f t="shared" si="17"/>
+        <v>27600</v>
+      </c>
+      <c r="L109" s="195">
         <v>0</v>
       </c>
       <c r="M109" s="8">
-        <f t="shared" si="18"/>
-        <v>25300.91</v>
+        <f t="shared" si="19"/>
+        <v>27600.91</v>
       </c>
       <c r="N109" s="8">
-        <f t="shared" si="19"/>
-        <v>26819.91</v>
+        <f t="shared" si="20"/>
+        <v>29257.91</v>
       </c>
       <c r="O109" s="141">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>0.91000000000000059</v>
       </c>
     </row>
@@ -11259,82 +11255,82 @@
         <v>23000.92</v>
       </c>
       <c r="H110" s="44">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>23000.92</v>
       </c>
       <c r="I110" s="159">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="J110" s="160">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="K110" s="160">
-        <f t="shared" si="16"/>
-        <v>25300</v>
-      </c>
-      <c r="L110" s="236">
+        <f t="shared" si="17"/>
+        <v>27600</v>
+      </c>
+      <c r="L110" s="195">
         <v>0</v>
       </c>
       <c r="M110" s="162">
-        <f t="shared" si="18"/>
-        <v>25300.92</v>
+        <f t="shared" si="19"/>
+        <v>27600.92</v>
       </c>
       <c r="N110" s="162">
-        <f t="shared" si="19"/>
-        <v>26819.919999999998</v>
+        <f t="shared" si="20"/>
+        <v>29257.919999999998</v>
       </c>
       <c r="O110" s="141">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>0.9200000000000006</v>
       </c>
     </row>
     <row r="111" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A111" s="114"/>
       <c r="B111" s="35"/>
-      <c r="C111" s="254" t="s">
+      <c r="C111" s="207" t="s">
         <v>150</v>
       </c>
-      <c r="D111" s="255" t="s">
+      <c r="D111" s="208" t="s">
         <v>197</v>
       </c>
-      <c r="E111" s="255"/>
-      <c r="F111" s="264">
+      <c r="E111" s="208"/>
+      <c r="F111" s="217">
         <v>2.3E-3</v>
       </c>
-      <c r="G111" s="258">
+      <c r="G111" s="211">
         <v>23000.93</v>
       </c>
-      <c r="H111" s="263">
-        <f t="shared" si="22"/>
+      <c r="H111" s="216">
+        <f t="shared" si="23"/>
         <v>23000.93</v>
       </c>
-      <c r="I111" s="259">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="J111" s="260">
-        <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="K111" s="260">
+      <c r="I111" s="212">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J111" s="213">
         <f t="shared" si="16"/>
-        <v>25300</v>
-      </c>
-      <c r="L111" s="261">
-        <v>0</v>
-      </c>
-      <c r="M111" s="262">
-        <f t="shared" si="18"/>
-        <v>25300.93</v>
-      </c>
-      <c r="N111" s="262">
+        <v>0</v>
+      </c>
+      <c r="K111" s="213">
+        <f t="shared" si="17"/>
+        <v>27600</v>
+      </c>
+      <c r="L111" s="214">
+        <v>0</v>
+      </c>
+      <c r="M111" s="215">
         <f t="shared" si="19"/>
-        <v>26819.93</v>
+        <v>27600.93</v>
+      </c>
+      <c r="N111" s="215">
+        <f t="shared" si="20"/>
+        <v>29257.93</v>
       </c>
       <c r="O111" s="141">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>0.9300000000000006</v>
       </c>
     </row>
@@ -11359,30 +11355,30 @@
         <v>6571.94</v>
       </c>
       <c r="I112" s="159">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="J112" s="160">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="K112" s="160">
-        <f t="shared" si="16"/>
-        <v>25300</v>
-      </c>
-      <c r="L112" s="236">
+        <f t="shared" si="17"/>
+        <v>27600</v>
+      </c>
+      <c r="L112" s="195">
         <v>0</v>
       </c>
       <c r="M112" s="162">
-        <f t="shared" si="18"/>
-        <v>25300.94</v>
+        <f t="shared" si="19"/>
+        <v>27600.94</v>
       </c>
       <c r="N112" s="162">
-        <f t="shared" si="19"/>
-        <v>26819.94</v>
+        <f t="shared" si="20"/>
+        <v>29257.94</v>
       </c>
       <c r="O112" s="141">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>0.94000000000000061</v>
       </c>
     </row>
@@ -11407,30 +11403,30 @@
         <v>23000.95</v>
       </c>
       <c r="I113" s="159">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="J113" s="160">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="K113" s="160">
-        <f t="shared" si="16"/>
-        <v>25300</v>
-      </c>
-      <c r="L113" s="236">
+        <f t="shared" si="17"/>
+        <v>27600</v>
+      </c>
+      <c r="L113" s="195">
         <v>0</v>
       </c>
       <c r="M113" s="162">
-        <f t="shared" si="18"/>
-        <v>25300.95</v>
+        <f t="shared" si="19"/>
+        <v>27600.95</v>
       </c>
       <c r="N113" s="162">
-        <f t="shared" si="19"/>
-        <v>26819.95</v>
+        <f t="shared" si="20"/>
+        <v>29257.95</v>
       </c>
       <c r="O113" s="141">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>0.95000000000000062</v>
       </c>
     </row>
@@ -11455,30 +11451,30 @@
         <v>20515.96</v>
       </c>
       <c r="I114" s="159">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="J114" s="160">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="K114" s="160">
-        <f t="shared" si="16"/>
-        <v>25300</v>
-      </c>
-      <c r="L114" s="236">
+        <f t="shared" si="17"/>
+        <v>27600</v>
+      </c>
+      <c r="L114" s="195">
         <v>0</v>
       </c>
       <c r="M114" s="162">
-        <f t="shared" si="18"/>
-        <v>25300.959999999999</v>
+        <f t="shared" si="19"/>
+        <v>27600.959999999999</v>
       </c>
       <c r="N114" s="162">
-        <f t="shared" si="19"/>
-        <v>26819.96</v>
+        <f t="shared" si="20"/>
+        <v>29257.96</v>
       </c>
       <c r="O114" s="141">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>0.96000000000000063</v>
       </c>
     </row>
@@ -11503,30 +11499,30 @@
         <v>23000.97</v>
       </c>
       <c r="I115" s="159">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="J115" s="160">
-        <f t="shared" ref="J115:J131" si="23">M$8*F115</f>
+        <f t="shared" ref="J115:J131" si="24">M$8*F115</f>
         <v>0</v>
       </c>
       <c r="K115" s="160">
-        <f t="shared" ref="K115:K131" si="24">M$2*F115</f>
-        <v>25300</v>
-      </c>
-      <c r="L115" s="236">
+        <f t="shared" ref="K115:K131" si="25">M$2*F115</f>
+        <v>27600</v>
+      </c>
+      <c r="L115" s="195">
         <v>0</v>
       </c>
       <c r="M115" s="162">
-        <f t="shared" si="18"/>
-        <v>25300.97</v>
+        <f t="shared" si="19"/>
+        <v>27600.97</v>
       </c>
       <c r="N115" s="162">
-        <f t="shared" si="19"/>
-        <v>26819.97</v>
+        <f t="shared" si="20"/>
+        <v>29257.97</v>
       </c>
       <c r="O115" s="141">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>0.97000000000000064</v>
       </c>
     </row>
@@ -11550,30 +11546,30 @@
         <v>20700.98</v>
       </c>
       <c r="I116" s="159">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>25624.000000000004</v>
       </c>
       <c r="J116" s="160">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="K116" s="160">
-        <f t="shared" si="24"/>
-        <v>25300</v>
-      </c>
-      <c r="L116" s="236">
+        <f t="shared" si="25"/>
+        <v>27600</v>
+      </c>
+      <c r="L116" s="195">
         <v>0</v>
       </c>
       <c r="M116" s="162">
-        <f t="shared" si="18"/>
-        <v>50924.98</v>
+        <f t="shared" si="19"/>
+        <v>53224.98</v>
       </c>
       <c r="N116" s="162">
-        <f t="shared" si="19"/>
-        <v>53980.98</v>
+        <f t="shared" si="20"/>
+        <v>56418.98</v>
       </c>
       <c r="O116" s="141">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>0.98000000000000065</v>
       </c>
     </row>
@@ -11595,30 +11591,30 @@
       </c>
       <c r="H117" s="44"/>
       <c r="I117" s="159">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>43701.99</v>
       </c>
       <c r="J117" s="160">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="K117" s="160">
-        <f t="shared" si="24"/>
-        <v>25300</v>
-      </c>
-      <c r="L117" s="236">
+        <f t="shared" si="25"/>
+        <v>27600</v>
+      </c>
+      <c r="L117" s="195">
         <v>0</v>
       </c>
       <c r="M117" s="162">
-        <f t="shared" si="18"/>
-        <v>69002.990000000005</v>
+        <f t="shared" si="19"/>
+        <v>71302.990000000005</v>
       </c>
       <c r="N117" s="162">
-        <f t="shared" si="19"/>
-        <v>73143.990000000005</v>
+        <f t="shared" si="20"/>
+        <v>75581.990000000005</v>
       </c>
       <c r="O117" s="141">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>0.99000000000000066</v>
       </c>
     </row>
@@ -11639,34 +11635,34 @@
         <v>23001</v>
       </c>
       <c r="H118" s="44">
-        <f t="shared" ref="H118" si="25">G118</f>
+        <f t="shared" ref="H118" si="26">G118</f>
         <v>23001</v>
       </c>
       <c r="I118" s="159">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="J118" s="160">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="K118" s="160">
-        <f t="shared" si="24"/>
-        <v>25300</v>
-      </c>
-      <c r="L118" s="236">
+        <f t="shared" si="25"/>
+        <v>27600</v>
+      </c>
+      <c r="L118" s="195">
         <v>0</v>
       </c>
       <c r="M118" s="162">
-        <f t="shared" si="18"/>
-        <v>25301</v>
+        <f t="shared" si="19"/>
+        <v>27601</v>
       </c>
       <c r="N118" s="162">
-        <f t="shared" si="19"/>
-        <v>26820</v>
+        <f t="shared" si="20"/>
+        <v>29258</v>
       </c>
       <c r="O118" s="141">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>1.0000000000000007</v>
       </c>
       <c r="P118" t="s">
@@ -11690,34 +11686,34 @@
         <v>23001.01</v>
       </c>
       <c r="H119" s="44">
-        <f t="shared" ref="H119:H122" si="26">G119</f>
+        <f t="shared" ref="H119:H122" si="27">G119</f>
         <v>23001.01</v>
       </c>
       <c r="I119" s="159">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="J119" s="160">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="K119" s="160">
-        <f t="shared" si="24"/>
-        <v>25300</v>
-      </c>
-      <c r="L119" s="236">
+        <f t="shared" si="25"/>
+        <v>27600</v>
+      </c>
+      <c r="L119" s="195">
         <v>0</v>
       </c>
       <c r="M119" s="162">
-        <f t="shared" si="18"/>
-        <v>25301.01</v>
+        <f t="shared" si="19"/>
+        <v>27601.01</v>
       </c>
       <c r="N119" s="162">
-        <f t="shared" si="19"/>
-        <v>26820.01</v>
+        <f t="shared" si="20"/>
+        <v>29258.01</v>
       </c>
       <c r="O119" s="141">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>1.0100000000000007</v>
       </c>
     </row>
@@ -11742,77 +11738,77 @@
         <v>23000.1</v>
       </c>
       <c r="I120" s="159">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0.92000000000189175</v>
       </c>
       <c r="J120" s="160">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="K120" s="160">
-        <f t="shared" si="24"/>
-        <v>25300</v>
-      </c>
-      <c r="L120" s="236">
+        <f t="shared" si="25"/>
+        <v>27600</v>
+      </c>
+      <c r="L120" s="195">
         <v>0</v>
       </c>
       <c r="M120" s="162">
-        <f t="shared" si="18"/>
-        <v>25302.02</v>
+        <f t="shared" si="19"/>
+        <v>27602.02</v>
       </c>
       <c r="N120" s="162">
-        <f t="shared" si="19"/>
-        <v>26821.02</v>
+        <f t="shared" si="20"/>
+        <v>29259.02</v>
       </c>
       <c r="O120" s="141">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>1.0200000000000007</v>
       </c>
     </row>
     <row r="121" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A121" s="135"/>
       <c r="B121" s="35"/>
-      <c r="C121" s="238" t="s">
+      <c r="C121" s="197" t="s">
         <v>160</v>
       </c>
-      <c r="D121" s="239" t="s">
+      <c r="D121" s="198" t="s">
         <v>185</v>
       </c>
-      <c r="E121" s="239"/>
-      <c r="F121" s="253">
+      <c r="E121" s="198"/>
+      <c r="F121" s="206">
         <v>2.3E-3</v>
       </c>
-      <c r="G121" s="242">
+      <c r="G121" s="201">
         <v>43702.03</v>
       </c>
-      <c r="H121" s="270">
+      <c r="H121" s="220">
         <v>23000</v>
       </c>
-      <c r="I121" s="243">
-        <f t="shared" si="0"/>
+      <c r="I121" s="202">
+        <f t="shared" si="1"/>
         <v>20702.03</v>
       </c>
-      <c r="J121" s="244">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
-      <c r="K121" s="244">
+      <c r="J121" s="203">
         <f t="shared" si="24"/>
-        <v>25300</v>
-      </c>
-      <c r="L121" s="245">
-        <v>0</v>
-      </c>
-      <c r="M121" s="246">
-        <f t="shared" si="18"/>
-        <v>46003.03</v>
-      </c>
-      <c r="N121" s="246">
+        <v>0</v>
+      </c>
+      <c r="K121" s="203">
+        <f t="shared" si="25"/>
+        <v>27600</v>
+      </c>
+      <c r="L121" s="204">
+        <v>0</v>
+      </c>
+      <c r="M121" s="205">
         <f t="shared" si="19"/>
-        <v>48764.03</v>
+        <v>48303.03</v>
+      </c>
+      <c r="N121" s="205">
+        <f t="shared" si="20"/>
+        <v>51202.03</v>
       </c>
       <c r="O121" s="141">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>1.0300000000000007</v>
       </c>
     </row>
@@ -11833,34 +11829,34 @@
         <v>23001.040000000001</v>
       </c>
       <c r="H122" s="90">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>23001.040000000001</v>
       </c>
       <c r="I122" s="56">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="J122" s="26">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="K122" s="26">
-        <f t="shared" si="24"/>
-        <v>25300</v>
-      </c>
-      <c r="L122" s="236">
+        <f t="shared" si="25"/>
+        <v>27600</v>
+      </c>
+      <c r="L122" s="195">
         <v>0</v>
       </c>
       <c r="M122" s="8">
-        <f t="shared" si="18"/>
-        <v>25301.040000000001</v>
+        <f t="shared" si="19"/>
+        <v>27601.040000000001</v>
       </c>
       <c r="N122" s="8">
-        <f t="shared" si="19"/>
-        <v>26820.04</v>
+        <f t="shared" si="20"/>
+        <v>29258.04</v>
       </c>
       <c r="O122" s="141">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>1.0400000000000007</v>
       </c>
     </row>
@@ -11885,30 +11881,30 @@
         <v>38180</v>
       </c>
       <c r="I123" s="56">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>5522.0500000000029</v>
       </c>
       <c r="J123" s="26">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="K123" s="26">
-        <f t="shared" si="24"/>
-        <v>25300</v>
-      </c>
-      <c r="L123" s="236">
+        <f t="shared" si="25"/>
+        <v>27600</v>
+      </c>
+      <c r="L123" s="195">
         <v>0</v>
       </c>
       <c r="M123" s="8">
-        <f t="shared" si="18"/>
-        <v>30823.05</v>
+        <f t="shared" si="19"/>
+        <v>33123.050000000003</v>
       </c>
       <c r="N123" s="8">
-        <f t="shared" si="19"/>
-        <v>32673.05</v>
+        <f t="shared" si="20"/>
+        <v>35111.050000000003</v>
       </c>
       <c r="O123" s="141">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>1.0500000000000007</v>
       </c>
     </row>
@@ -11930,30 +11926,30 @@
       </c>
       <c r="H124" s="90"/>
       <c r="I124" s="56">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>43702.06</v>
       </c>
       <c r="J124" s="26">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="K124" s="26">
-        <f t="shared" si="24"/>
-        <v>25300</v>
-      </c>
-      <c r="L124" s="236">
+        <f t="shared" si="25"/>
+        <v>27600</v>
+      </c>
+      <c r="L124" s="195">
         <v>0</v>
       </c>
       <c r="M124" s="8">
-        <f t="shared" si="18"/>
-        <v>69003.06</v>
+        <f t="shared" si="19"/>
+        <v>71303.06</v>
       </c>
       <c r="N124" s="8">
-        <f t="shared" si="19"/>
-        <v>73144.06</v>
+        <f t="shared" si="20"/>
+        <v>75582.06</v>
       </c>
       <c r="O124" s="141">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>1.0600000000000007</v>
       </c>
     </row>
@@ -11975,78 +11971,78 @@
       </c>
       <c r="H125" s="90"/>
       <c r="I125" s="56">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>43702.07</v>
       </c>
       <c r="J125" s="26">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="K125" s="26">
-        <f t="shared" si="24"/>
-        <v>25300</v>
-      </c>
-      <c r="L125" s="236">
+        <f t="shared" si="25"/>
+        <v>27600</v>
+      </c>
+      <c r="L125" s="195">
         <v>0</v>
       </c>
       <c r="M125" s="8">
-        <f t="shared" si="18"/>
-        <v>69003.070000000007</v>
+        <f t="shared" si="19"/>
+        <v>71303.070000000007</v>
       </c>
       <c r="N125" s="8">
-        <f t="shared" si="19"/>
-        <v>73144.070000000007</v>
+        <f t="shared" si="20"/>
+        <v>75582.070000000007</v>
       </c>
       <c r="O125" s="141">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>1.0700000000000007</v>
       </c>
     </row>
     <row r="126" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A126" s="135"/>
       <c r="B126" s="35"/>
-      <c r="C126" s="254" t="s">
+      <c r="C126" s="207" t="s">
         <v>165</v>
       </c>
-      <c r="D126" s="255" t="s">
+      <c r="D126" s="208" t="s">
         <v>185</v>
       </c>
-      <c r="E126" s="255"/>
-      <c r="F126" s="264">
+      <c r="E126" s="208"/>
+      <c r="F126" s="217">
         <v>2.3E-3</v>
       </c>
-      <c r="G126" s="258">
+      <c r="G126" s="211">
         <v>43702.080000000002</v>
       </c>
-      <c r="H126" s="263">
-        <f>G126</f>
+      <c r="H126" s="216">
+        <f t="shared" ref="H126:H131" si="28">G126</f>
         <v>43702.080000000002</v>
       </c>
-      <c r="I126" s="259">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="J126" s="260">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
-      <c r="K126" s="260">
+      <c r="I126" s="212">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J126" s="213">
         <f t="shared" si="24"/>
-        <v>25300</v>
-      </c>
-      <c r="L126" s="261">
-        <v>0</v>
-      </c>
-      <c r="M126" s="262">
-        <f t="shared" si="18"/>
-        <v>25301.08</v>
-      </c>
-      <c r="N126" s="262">
+        <v>0</v>
+      </c>
+      <c r="K126" s="213">
+        <f t="shared" si="25"/>
+        <v>27600</v>
+      </c>
+      <c r="L126" s="214">
+        <v>0</v>
+      </c>
+      <c r="M126" s="215">
         <f t="shared" si="19"/>
-        <v>26820.080000000002</v>
+        <v>27601.08</v>
+      </c>
+      <c r="N126" s="215">
+        <f t="shared" si="20"/>
+        <v>29258.080000000002</v>
       </c>
       <c r="O126" s="141">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>1.0800000000000007</v>
       </c>
     </row>
@@ -12067,34 +12063,34 @@
         <v>23001.09</v>
       </c>
       <c r="H127" s="90">
-        <f>G127</f>
+        <f t="shared" si="28"/>
         <v>23001.09</v>
       </c>
       <c r="I127" s="56">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="J127" s="26">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="K127" s="26">
-        <f t="shared" si="24"/>
-        <v>25300</v>
-      </c>
-      <c r="L127" s="236">
+        <f t="shared" si="25"/>
+        <v>27600</v>
+      </c>
+      <c r="L127" s="195">
         <v>0</v>
       </c>
       <c r="M127" s="8">
-        <f t="shared" si="18"/>
-        <v>25301.09</v>
+        <f t="shared" si="19"/>
+        <v>27601.09</v>
       </c>
       <c r="N127" s="8">
-        <f t="shared" si="19"/>
-        <v>26820.09</v>
+        <f t="shared" si="20"/>
+        <v>29258.09</v>
       </c>
       <c r="O127" s="141">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>1.0900000000000007</v>
       </c>
     </row>
@@ -12115,34 +12111,34 @@
         <v>21758.1</v>
       </c>
       <c r="H128" s="90">
-        <f>G128</f>
+        <f t="shared" si="28"/>
         <v>21758.1</v>
       </c>
       <c r="I128" s="56">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="J128" s="26">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="K128" s="26">
-        <f t="shared" si="24"/>
-        <v>25300</v>
-      </c>
-      <c r="L128" s="236">
+        <f t="shared" si="25"/>
+        <v>27600</v>
+      </c>
+      <c r="L128" s="195">
         <v>0</v>
       </c>
       <c r="M128" s="8">
-        <f t="shared" si="18"/>
-        <v>25301.1</v>
+        <f t="shared" si="19"/>
+        <v>27601.1</v>
       </c>
       <c r="N128" s="8">
-        <f t="shared" si="19"/>
-        <v>26820.1</v>
+        <f t="shared" si="20"/>
+        <v>29258.1</v>
       </c>
       <c r="O128" s="141">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>1.1000000000000008</v>
       </c>
     </row>
@@ -12163,34 +12159,34 @@
         <v>23001.11</v>
       </c>
       <c r="H129" s="90">
-        <f>G129</f>
+        <f t="shared" si="28"/>
         <v>23001.11</v>
       </c>
       <c r="I129" s="56">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="J129" s="26">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="K129" s="26">
-        <f t="shared" si="24"/>
-        <v>25300</v>
-      </c>
-      <c r="L129" s="236">
+        <f t="shared" si="25"/>
+        <v>27600</v>
+      </c>
+      <c r="L129" s="195">
         <v>0</v>
       </c>
       <c r="M129" s="8">
-        <f t="shared" si="18"/>
-        <v>25301.11</v>
+        <f t="shared" si="19"/>
+        <v>27601.11</v>
       </c>
       <c r="N129" s="8">
-        <f t="shared" si="19"/>
-        <v>26820.11</v>
+        <f t="shared" si="20"/>
+        <v>29258.11</v>
       </c>
       <c r="O129" s="141">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>1.1100000000000008</v>
       </c>
     </row>
@@ -12213,34 +12209,34 @@
         <v>23001.119999999999</v>
       </c>
       <c r="H130" s="90">
-        <f>G130</f>
+        <f t="shared" si="28"/>
         <v>23001.119999999999</v>
       </c>
       <c r="I130" s="56">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="J130" s="26">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="K130" s="26">
-        <f t="shared" si="24"/>
-        <v>25300</v>
-      </c>
-      <c r="L130" s="236">
+        <f t="shared" si="25"/>
+        <v>27600</v>
+      </c>
+      <c r="L130" s="195">
         <v>0</v>
       </c>
       <c r="M130" s="8">
-        <f t="shared" si="18"/>
-        <v>25301.119999999999</v>
+        <f t="shared" si="19"/>
+        <v>27601.119999999999</v>
       </c>
       <c r="N130" s="8">
-        <f t="shared" si="19"/>
-        <v>26820.12</v>
+        <f t="shared" si="20"/>
+        <v>29258.12</v>
       </c>
       <c r="O130" s="141">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>1.1200000000000008</v>
       </c>
     </row>
@@ -12263,34 +12259,34 @@
         <v>23001.13</v>
       </c>
       <c r="H131" s="90">
-        <f>G131</f>
+        <f t="shared" si="28"/>
         <v>23001.13</v>
       </c>
       <c r="I131" s="56">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="J131" s="26">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="K131" s="26">
-        <f t="shared" si="24"/>
-        <v>25300</v>
-      </c>
-      <c r="L131" s="236">
+        <f t="shared" si="25"/>
+        <v>27600</v>
+      </c>
+      <c r="L131" s="195">
         <v>0</v>
       </c>
       <c r="M131" s="8">
-        <f t="shared" si="18"/>
-        <v>25301.13</v>
+        <f t="shared" si="19"/>
+        <v>27601.13</v>
       </c>
       <c r="N131" s="8">
-        <f t="shared" si="19"/>
-        <v>26820.13</v>
+        <f t="shared" si="20"/>
+        <v>29258.13</v>
       </c>
       <c r="O131" s="141">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>1.1300000000000008</v>
       </c>
     </row>
@@ -12337,55 +12333,55 @@
       </c>
       <c r="K133" s="28">
         <f>SUM(K14:K132)</f>
-        <v>10947157.55484</v>
-      </c>
-      <c r="L133" s="269">
+        <v>11945157.55484</v>
+      </c>
+      <c r="L133" s="219">
         <f>SUM(L14:L132)</f>
         <v>206000</v>
       </c>
       <c r="M133" s="29">
         <f>SUM(M14:M132)</f>
-        <v>13333953.964839999</v>
+        <v>14331953.964839999</v>
       </c>
       <c r="N133" s="28">
         <f>SUM(N14:N132)</f>
-        <v>14134049.4181304</v>
+        <v>15191929.4181304</v>
       </c>
       <c r="P133" s="59"/>
     </row>
     <row r="134" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="K134" s="61">
         <f>K133-L1</f>
-        <v>1338773.6948400009</v>
+        <v>2336773.6948400009</v>
       </c>
     </row>
     <row r="135" spans="1:16" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C135" s="197"/>
-      <c r="D135" s="197"/>
-      <c r="E135" s="197"/>
-      <c r="F135" s="197"/>
-      <c r="G135" s="197"/>
-      <c r="H135" s="197"/>
-      <c r="I135" s="197"/>
-      <c r="J135" s="197"/>
-      <c r="K135" s="197"/>
-      <c r="L135" s="197"/>
-      <c r="M135" s="197"/>
-      <c r="N135" s="197"/>
+      <c r="C135" s="250"/>
+      <c r="D135" s="250"/>
+      <c r="E135" s="250"/>
+      <c r="F135" s="250"/>
+      <c r="G135" s="250"/>
+      <c r="H135" s="250"/>
+      <c r="I135" s="250"/>
+      <c r="J135" s="250"/>
+      <c r="K135" s="250"/>
+      <c r="L135" s="250"/>
+      <c r="M135" s="250"/>
+      <c r="N135" s="250"/>
     </row>
     <row r="136" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
-      <c r="C136" s="197"/>
-      <c r="D136" s="197"/>
-      <c r="E136" s="197"/>
-      <c r="F136" s="197"/>
-      <c r="G136" s="197"/>
-      <c r="H136" s="197"/>
-      <c r="I136" s="197"/>
-      <c r="J136" s="197"/>
-      <c r="K136" s="197"/>
-      <c r="L136" s="197"/>
-      <c r="M136" s="197"/>
-      <c r="N136" s="197"/>
+      <c r="C136" s="250"/>
+      <c r="D136" s="250"/>
+      <c r="E136" s="250"/>
+      <c r="F136" s="250"/>
+      <c r="G136" s="250"/>
+      <c r="H136" s="250"/>
+      <c r="I136" s="250"/>
+      <c r="J136" s="250"/>
+      <c r="K136" s="250"/>
+      <c r="L136" s="250"/>
+      <c r="M136" s="250"/>
+      <c r="N136" s="250"/>
     </row>
     <row r="137" spans="1:16" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C137" s="79"/>
@@ -12402,118 +12398,118 @@
       <c r="N137" s="79"/>
     </row>
     <row r="138" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="C138" s="197" t="s">
+      <c r="C138" s="250" t="s">
         <v>265</v>
       </c>
-      <c r="D138" s="197"/>
-      <c r="E138" s="197"/>
-      <c r="F138" s="197"/>
-      <c r="G138" s="197"/>
-      <c r="H138" s="197"/>
-      <c r="I138" s="197"/>
-      <c r="J138" s="197"/>
-      <c r="K138" s="197"/>
-      <c r="L138" s="197"/>
-      <c r="M138" s="197"/>
-      <c r="N138" s="197"/>
+      <c r="D138" s="250"/>
+      <c r="E138" s="250"/>
+      <c r="F138" s="250"/>
+      <c r="G138" s="250"/>
+      <c r="H138" s="250"/>
+      <c r="I138" s="250"/>
+      <c r="J138" s="250"/>
+      <c r="K138" s="250"/>
+      <c r="L138" s="250"/>
+      <c r="M138" s="250"/>
+      <c r="N138" s="250"/>
     </row>
     <row r="139" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="C139" s="197"/>
-      <c r="D139" s="197"/>
-      <c r="E139" s="197"/>
-      <c r="F139" s="197"/>
-      <c r="G139" s="197"/>
-      <c r="H139" s="197"/>
-      <c r="I139" s="197"/>
-      <c r="J139" s="197"/>
-      <c r="K139" s="197"/>
-      <c r="L139" s="197"/>
-      <c r="M139" s="197"/>
-      <c r="N139" s="197"/>
+      <c r="C139" s="250"/>
+      <c r="D139" s="250"/>
+      <c r="E139" s="250"/>
+      <c r="F139" s="250"/>
+      <c r="G139" s="250"/>
+      <c r="H139" s="250"/>
+      <c r="I139" s="250"/>
+      <c r="J139" s="250"/>
+      <c r="K139" s="250"/>
+      <c r="L139" s="250"/>
+      <c r="M139" s="250"/>
+      <c r="N139" s="250"/>
     </row>
     <row r="140" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="C140" s="197"/>
-      <c r="D140" s="197"/>
-      <c r="E140" s="197"/>
-      <c r="F140" s="197"/>
-      <c r="G140" s="197"/>
-      <c r="H140" s="197"/>
-      <c r="I140" s="197"/>
-      <c r="J140" s="197"/>
-      <c r="K140" s="197"/>
-      <c r="L140" s="197"/>
-      <c r="M140" s="197"/>
-      <c r="N140" s="197"/>
+      <c r="C140" s="250"/>
+      <c r="D140" s="250"/>
+      <c r="E140" s="250"/>
+      <c r="F140" s="250"/>
+      <c r="G140" s="250"/>
+      <c r="H140" s="250"/>
+      <c r="I140" s="250"/>
+      <c r="J140" s="250"/>
+      <c r="K140" s="250"/>
+      <c r="L140" s="250"/>
+      <c r="M140" s="250"/>
+      <c r="N140" s="250"/>
     </row>
     <row r="141" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="C141" s="197"/>
-      <c r="D141" s="197"/>
-      <c r="E141" s="197"/>
-      <c r="F141" s="197"/>
-      <c r="G141" s="197"/>
-      <c r="H141" s="197"/>
-      <c r="I141" s="197"/>
-      <c r="J141" s="197"/>
-      <c r="K141" s="197"/>
-      <c r="L141" s="197"/>
-      <c r="M141" s="197"/>
-      <c r="N141" s="197"/>
+      <c r="C141" s="250"/>
+      <c r="D141" s="250"/>
+      <c r="E141" s="250"/>
+      <c r="F141" s="250"/>
+      <c r="G141" s="250"/>
+      <c r="H141" s="250"/>
+      <c r="I141" s="250"/>
+      <c r="J141" s="250"/>
+      <c r="K141" s="250"/>
+      <c r="L141" s="250"/>
+      <c r="M141" s="250"/>
+      <c r="N141" s="250"/>
     </row>
     <row r="142" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="C142" s="197"/>
-      <c r="D142" s="197"/>
-      <c r="E142" s="197"/>
-      <c r="F142" s="197"/>
-      <c r="G142" s="197"/>
-      <c r="H142" s="197"/>
-      <c r="I142" s="197"/>
-      <c r="J142" s="197"/>
-      <c r="K142" s="197"/>
-      <c r="L142" s="197"/>
-      <c r="M142" s="197"/>
-      <c r="N142" s="197"/>
+      <c r="C142" s="250"/>
+      <c r="D142" s="250"/>
+      <c r="E142" s="250"/>
+      <c r="F142" s="250"/>
+      <c r="G142" s="250"/>
+      <c r="H142" s="250"/>
+      <c r="I142" s="250"/>
+      <c r="J142" s="250"/>
+      <c r="K142" s="250"/>
+      <c r="L142" s="250"/>
+      <c r="M142" s="250"/>
+      <c r="N142" s="250"/>
     </row>
     <row r="143" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="C143" s="197"/>
-      <c r="D143" s="197"/>
-      <c r="E143" s="197"/>
-      <c r="F143" s="197"/>
-      <c r="G143" s="197"/>
-      <c r="H143" s="197"/>
-      <c r="I143" s="197"/>
-      <c r="J143" s="197"/>
-      <c r="K143" s="197"/>
-      <c r="L143" s="197"/>
-      <c r="M143" s="197"/>
-      <c r="N143" s="197"/>
+      <c r="C143" s="250"/>
+      <c r="D143" s="250"/>
+      <c r="E143" s="250"/>
+      <c r="F143" s="250"/>
+      <c r="G143" s="250"/>
+      <c r="H143" s="250"/>
+      <c r="I143" s="250"/>
+      <c r="J143" s="250"/>
+      <c r="K143" s="250"/>
+      <c r="L143" s="250"/>
+      <c r="M143" s="250"/>
+      <c r="N143" s="250"/>
     </row>
     <row r="144" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="C144" s="197"/>
-      <c r="D144" s="197"/>
-      <c r="E144" s="197"/>
-      <c r="F144" s="197"/>
-      <c r="G144" s="197"/>
-      <c r="H144" s="197"/>
-      <c r="I144" s="197"/>
-      <c r="J144" s="197"/>
-      <c r="K144" s="197"/>
-      <c r="L144" s="197"/>
-      <c r="M144" s="197"/>
-      <c r="N144" s="197"/>
+      <c r="C144" s="250"/>
+      <c r="D144" s="250"/>
+      <c r="E144" s="250"/>
+      <c r="F144" s="250"/>
+      <c r="G144" s="250"/>
+      <c r="H144" s="250"/>
+      <c r="I144" s="250"/>
+      <c r="J144" s="250"/>
+      <c r="K144" s="250"/>
+      <c r="L144" s="250"/>
+      <c r="M144" s="250"/>
+      <c r="N144" s="250"/>
     </row>
     <row r="145" spans="3:16" x14ac:dyDescent="0.25">
-      <c r="C145" s="197"/>
-      <c r="D145" s="197"/>
-      <c r="E145" s="197"/>
-      <c r="F145" s="197"/>
-      <c r="G145" s="197"/>
-      <c r="H145" s="197"/>
-      <c r="I145" s="197"/>
-      <c r="J145" s="197"/>
-      <c r="K145" s="197"/>
-      <c r="L145" s="197"/>
-      <c r="M145" s="197"/>
-      <c r="N145" s="197"/>
+      <c r="C145" s="250"/>
+      <c r="D145" s="250"/>
+      <c r="E145" s="250"/>
+      <c r="F145" s="250"/>
+      <c r="G145" s="250"/>
+      <c r="H145" s="250"/>
+      <c r="I145" s="250"/>
+      <c r="J145" s="250"/>
+      <c r="K145" s="250"/>
+      <c r="L145" s="250"/>
+      <c r="M145" s="250"/>
+      <c r="N145" s="250"/>
     </row>
     <row r="146" spans="3:16" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C146" s="79"/>
@@ -12544,117 +12540,111 @@
       <c r="N147" s="79"/>
     </row>
     <row r="148" spans="3:16" x14ac:dyDescent="0.25">
-      <c r="C148" s="196" t="s">
+      <c r="C148" s="249" t="s">
         <v>264</v>
       </c>
-      <c r="D148" s="196"/>
-      <c r="E148" s="196"/>
-      <c r="F148" s="196"/>
-      <c r="G148" s="196"/>
-      <c r="H148" s="196"/>
-      <c r="I148" s="196"/>
-      <c r="J148" s="196"/>
-      <c r="K148" s="196"/>
-      <c r="L148" s="196"/>
-      <c r="M148" s="196"/>
-      <c r="N148" s="196"/>
+      <c r="D148" s="249"/>
+      <c r="E148" s="249"/>
+      <c r="F148" s="249"/>
+      <c r="G148" s="249"/>
+      <c r="H148" s="249"/>
+      <c r="I148" s="249"/>
+      <c r="J148" s="249"/>
+      <c r="K148" s="249"/>
+      <c r="L148" s="249"/>
+      <c r="M148" s="249"/>
+      <c r="N148" s="249"/>
     </row>
     <row r="149" spans="3:16" x14ac:dyDescent="0.25">
-      <c r="C149" s="196"/>
-      <c r="D149" s="196"/>
-      <c r="E149" s="196"/>
-      <c r="F149" s="196"/>
-      <c r="G149" s="196"/>
-      <c r="H149" s="196"/>
-      <c r="I149" s="196"/>
-      <c r="J149" s="196"/>
-      <c r="K149" s="196"/>
-      <c r="L149" s="196"/>
-      <c r="M149" s="196"/>
-      <c r="N149" s="196"/>
+      <c r="C149" s="249"/>
+      <c r="D149" s="249"/>
+      <c r="E149" s="249"/>
+      <c r="F149" s="249"/>
+      <c r="G149" s="249"/>
+      <c r="H149" s="249"/>
+      <c r="I149" s="249"/>
+      <c r="J149" s="249"/>
+      <c r="K149" s="249"/>
+      <c r="L149" s="249"/>
+      <c r="M149" s="249"/>
+      <c r="N149" s="249"/>
     </row>
     <row r="150" spans="3:16" x14ac:dyDescent="0.25">
-      <c r="C150" s="196"/>
-      <c r="D150" s="196"/>
-      <c r="E150" s="196"/>
-      <c r="F150" s="196"/>
-      <c r="G150" s="196"/>
-      <c r="H150" s="196"/>
-      <c r="I150" s="196"/>
-      <c r="J150" s="196"/>
-      <c r="K150" s="196"/>
-      <c r="L150" s="196"/>
-      <c r="M150" s="196"/>
-      <c r="N150" s="196"/>
+      <c r="C150" s="249"/>
+      <c r="D150" s="249"/>
+      <c r="E150" s="249"/>
+      <c r="F150" s="249"/>
+      <c r="G150" s="249"/>
+      <c r="H150" s="249"/>
+      <c r="I150" s="249"/>
+      <c r="J150" s="249"/>
+      <c r="K150" s="249"/>
+      <c r="L150" s="249"/>
+      <c r="M150" s="249"/>
+      <c r="N150" s="249"/>
       <c r="P150" s="86">
         <f>L1-K133</f>
-        <v>-1338773.6948400009</v>
+        <v>-2336773.6948400009</v>
       </c>
     </row>
     <row r="151" spans="3:16" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C151" s="196"/>
-      <c r="D151" s="196"/>
-      <c r="E151" s="196"/>
-      <c r="F151" s="196"/>
-      <c r="G151" s="196"/>
-      <c r="H151" s="196"/>
-      <c r="I151" s="196"/>
-      <c r="J151" s="196"/>
-      <c r="K151" s="196"/>
-      <c r="L151" s="196"/>
-      <c r="M151" s="196"/>
-      <c r="N151" s="196"/>
+      <c r="C151" s="249"/>
+      <c r="D151" s="249"/>
+      <c r="E151" s="249"/>
+      <c r="F151" s="249"/>
+      <c r="G151" s="249"/>
+      <c r="H151" s="249"/>
+      <c r="I151" s="249"/>
+      <c r="J151" s="249"/>
+      <c r="K151" s="249"/>
+      <c r="L151" s="249"/>
+      <c r="M151" s="249"/>
+      <c r="N151" s="249"/>
     </row>
     <row r="152" spans="3:16" ht="5.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C152" s="196"/>
-      <c r="D152" s="196"/>
-      <c r="E152" s="196"/>
-      <c r="F152" s="196"/>
-      <c r="G152" s="196"/>
-      <c r="H152" s="196"/>
-      <c r="I152" s="196"/>
-      <c r="J152" s="196"/>
-      <c r="K152" s="196"/>
-      <c r="L152" s="196"/>
-      <c r="M152" s="196"/>
-      <c r="N152" s="196"/>
+      <c r="C152" s="249"/>
+      <c r="D152" s="249"/>
+      <c r="E152" s="249"/>
+      <c r="F152" s="249"/>
+      <c r="G152" s="249"/>
+      <c r="H152" s="249"/>
+      <c r="I152" s="249"/>
+      <c r="J152" s="249"/>
+      <c r="K152" s="249"/>
+      <c r="L152" s="249"/>
+      <c r="M152" s="249"/>
+      <c r="N152" s="249"/>
     </row>
     <row r="153" spans="3:16" hidden="1" x14ac:dyDescent="0.25">
-      <c r="C153" s="196"/>
-      <c r="D153" s="196"/>
-      <c r="E153" s="196"/>
-      <c r="F153" s="196"/>
-      <c r="G153" s="196"/>
-      <c r="H153" s="196"/>
-      <c r="I153" s="196"/>
-      <c r="J153" s="196"/>
-      <c r="K153" s="196"/>
-      <c r="L153" s="196"/>
-      <c r="M153" s="196"/>
-      <c r="N153" s="196"/>
+      <c r="C153" s="249"/>
+      <c r="D153" s="249"/>
+      <c r="E153" s="249"/>
+      <c r="F153" s="249"/>
+      <c r="G153" s="249"/>
+      <c r="H153" s="249"/>
+      <c r="I153" s="249"/>
+      <c r="J153" s="249"/>
+      <c r="K153" s="249"/>
+      <c r="L153" s="249"/>
+      <c r="M153" s="249"/>
+      <c r="N153" s="249"/>
     </row>
     <row r="154" spans="3:16" hidden="1" x14ac:dyDescent="0.25">
-      <c r="C154" s="196"/>
-      <c r="D154" s="196"/>
-      <c r="E154" s="196"/>
-      <c r="F154" s="196"/>
-      <c r="G154" s="196"/>
-      <c r="H154" s="196"/>
-      <c r="I154" s="196"/>
-      <c r="J154" s="196"/>
-      <c r="K154" s="196"/>
-      <c r="L154" s="196"/>
-      <c r="M154" s="196"/>
-      <c r="N154" s="196"/>
+      <c r="C154" s="249"/>
+      <c r="D154" s="249"/>
+      <c r="E154" s="249"/>
+      <c r="F154" s="249"/>
+      <c r="G154" s="249"/>
+      <c r="H154" s="249"/>
+      <c r="I154" s="249"/>
+      <c r="J154" s="249"/>
+      <c r="K154" s="249"/>
+      <c r="L154" s="249"/>
+      <c r="M154" s="249"/>
+      <c r="N154" s="249"/>
     </row>
   </sheetData>
   <mergeCells count="21">
-    <mergeCell ref="A11:A13"/>
-    <mergeCell ref="B11:B13"/>
-    <mergeCell ref="C11:C13"/>
-    <mergeCell ref="D11:D13"/>
-    <mergeCell ref="F11:F13"/>
-    <mergeCell ref="E11:E13"/>
     <mergeCell ref="Q14:R15"/>
     <mergeCell ref="G11:G13"/>
     <mergeCell ref="C148:N154"/>
@@ -12670,6 +12660,12 @@
     <mergeCell ref="N11:N12"/>
     <mergeCell ref="C5:N8"/>
     <mergeCell ref="C9:N10"/>
+    <mergeCell ref="A11:A13"/>
+    <mergeCell ref="B11:B13"/>
+    <mergeCell ref="C11:C13"/>
+    <mergeCell ref="D11:D13"/>
+    <mergeCell ref="F11:F13"/>
+    <mergeCell ref="E11:E13"/>
   </mergeCells>
   <phoneticPr fontId="17" type="noConversion"/>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -12700,10 +12696,10 @@
   </cols>
   <sheetData>
     <row r="4" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C4" s="209" t="s">
+      <c r="C4" s="275" t="s">
         <v>287</v>
       </c>
-      <c r="D4" s="209"/>
+      <c r="D4" s="275"/>
     </row>
     <row r="5" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C5" s="145">
